--- a/reconcile/storage/output/capacities_plot.xlsx
+++ b/reconcile/storage/output/capacities_plot.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K176"/>
+  <dimension ref="A1:K206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,12 +584,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Apulia</t>
+          <t>Andalusia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -599,12 +599,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>deployment</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>midsummer</t>
+          <t>totalenergies</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -613,12 +613,12 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>50</v>
+        <v>263</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" s="2" t="n">
-        <v>45474</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="5">
@@ -627,30 +627,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aragon</t>
+          <t>Apulia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>wind</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>rwe renewables europe and australia</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+          <t>midsummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>50</v>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" s="2" t="n">
+        <v>45474</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -668,26 +680,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stellantis</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>45627</v>
-      </c>
+          <t>rwe renewables europe and australia</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
     </row>
@@ -710,19 +718,23 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>stellantis catl</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+          <t>stellantis</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>45627</v>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
     </row>
@@ -732,12 +744,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Auvergne-Rhône-Alpes</t>
+          <t>Aragon</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -745,23 +757,19 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>verkor</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>44927</v>
-      </c>
+          <t>stellantis catl</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
     </row>
@@ -771,12 +779,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Baden-Wurttemberg</t>
+          <t>Auvergne-Rhône-Alpes</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -784,28 +792,24 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>cellforce</t>
+          <t>verkor</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" s="2" t="n">
-        <v>44682</v>
-      </c>
+        <v>0.15</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>44927</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -829,27 +833,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>recycling</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>fortum battery recycling</t>
+          <t>cellforce</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3000</v>
+        <v>1.3</v>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" s="2" t="n">
-        <v>45778</v>
-      </c>
+      <c r="J10" s="2" t="n">
+        <v>44682</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -872,19 +876,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>leclanche</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+          <t>fortum battery recycling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>3000</v>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" s="2" t="n">
+        <v>45778</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -902,13 +914,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>mercedes benz</t>
+          <t>leclanche</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -933,24 +949,36 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>nikola</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>mercedes benz</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>44621</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>45139</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>45566</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -968,31 +996,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>porsche</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>1.3</v>
-      </c>
+          <t>mercedes benz</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" s="2" t="n">
-        <v>45413</v>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1014,25 +1030,21 @@
           <t>vehicle</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>porsche</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>20000</v>
-      </c>
+          <t>nikola</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" s="2" t="n">
-        <v>43374</v>
-      </c>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1053,10 +1065,14 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>valmet automotive</t>
+          <t>porsche</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1064,10 +1080,12 @@
           <t>under construction</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>1.3</v>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" s="2" t="n">
-        <v>44228</v>
+        <v>45413</v>
       </c>
       <c r="K16" t="inlineStr"/>
     </row>
@@ -1077,42 +1095,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Basque Country</t>
+          <t>Baden-Wurttemberg</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>basquevolt</t>
+          <t>porsche</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>45078</v>
-      </c>
+        <v>20000</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" s="2" t="n">
+        <v>43374</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1125,7 +1139,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bavaria</t>
+          <t>Baden-Wurttemberg</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1135,12 +1149,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>primobius</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1148,12 +1162,12 @@
           <t>under construction</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" s="2" t="n">
-        <v>45170</v>
-      </c>
+      <c r="H18" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" s="2" t="n">
-        <v>45383</v>
+        <v>45292</v>
       </c>
       <c r="K18" t="inlineStr"/>
     </row>
@@ -1168,7 +1182,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bavaria</t>
+          <t>Baden-Wurttemberg</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1176,14 +1190,10 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>module_pack</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>valmet automotive</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1192,11 +1202,9 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" s="2" t="n">
-        <v>45170</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" s="2" t="n">
-        <v>45383</v>
+        <v>44228</v>
       </c>
       <c r="K19" t="inlineStr"/>
     </row>
@@ -1206,32 +1214,40 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bavaria</t>
+          <t>Basque Country</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>bmw</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+          <t>basquevolt</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>45078</v>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
     </row>
@@ -1241,32 +1257,40 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bavaria</t>
+          <t>Bauska Municipality</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>deployment</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>bmw</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+          <t>ignitis renewables</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>145</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>45839</v>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
     </row>
@@ -1289,25 +1313,29 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>fenecon</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" s="2" t="n">
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" s="2" t="n">
+        <v>45170</v>
+      </c>
+      <c r="J22" s="2" t="n">
         <v>45383</v>
       </c>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1328,16 +1356,28 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>module_pack</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>kion battery systems</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>bmw</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="I23" s="2" t="n">
+        <v>45170</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>45383</v>
+      </c>
       <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1356,34 +1396,24 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>man</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>45597</v>
-      </c>
+          <t>bmw</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" s="2" t="n">
-        <v>45748</v>
-      </c>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -1401,26 +1431,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>solar</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>fossil</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>sunrock</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>14</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>45566</v>
-      </c>
+          <t>bmw</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
     </row>
@@ -1445,12 +1471,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>recycling</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>tozero</t>
+          <t>fenecon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1458,11 +1484,13 @@
           <t>operational</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="n">
+        <v>0.025</v>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" s="2" t="n">
-        <v>45231</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="27">
@@ -1471,12 +1499,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Borsod-Abaúj-Zemplén</t>
+          <t>Bavaria</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1484,27 +1512,15 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>recycling</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>andrada group</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>45139</v>
-      </c>
+          <t>kion battery systems</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
     </row>
@@ -1519,7 +1535,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brandenburg</t>
+          <t>Bavaria</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1529,12 +1545,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>basf</t>
+          <t>man</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1543,16 +1559,14 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45292</v>
-      </c>
-      <c r="J28" s="2" t="n">
-        <v>43983</v>
-      </c>
+        <v>45597</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" s="2" t="n">
-        <v>45078</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="29">
@@ -1566,37 +1580,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brandenburg</t>
+          <t>Bavaria</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>module_pack</t>
-        </is>
-      </c>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>microvast gmbh</t>
+          <t>sunrock</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45566</v>
+      </c>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" s="2" t="n">
-        <v>44228</v>
-      </c>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -1609,22 +1619,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brandenburg</t>
+          <t>Bavaria</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>module</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>oxford pv</t>
+          <t>tozero</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1632,13 +1642,11 @@
           <t>operational</t>
         </is>
       </c>
-      <c r="H30" t="n">
-        <v>100</v>
-      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" s="2" t="n">
-        <v>45536</v>
+        <v>45231</v>
       </c>
     </row>
     <row r="31">
@@ -1647,12 +1655,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brandenburg</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1662,19 +1670,27 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>svolt</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+          <t>emr</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>2000</v>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" s="2" t="n">
+        <v>45536</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -1682,12 +1698,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brandenburg</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1697,12 +1713,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>tesla</t>
+          <t>veolia</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1711,10 +1727,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>50</v>
+        <v>0.001</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>44197</v>
+        <v>44562</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -1725,46 +1741,42 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brandenburg</t>
+          <t>Borsod-Abaúj-Zemplén</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>tesla</t>
+          <t>andrada group</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>500000</v>
+        <v>10000</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>43800</v>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>44256</v>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>44621</v>
-      </c>
+        <v>45139</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -1772,12 +1784,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bratislava Region</t>
+          <t>Brandenburg</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1787,27 +1799,31 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>inobat</t>
+          <t>basf</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>10</v>
+        <v>15000</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>44105</v>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+        <v>44713</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>43983</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>45078</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -1815,38 +1831,46 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bratislava Region</t>
+          <t>Brandenburg</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>recycling</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>basf</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>200000</v>
+        <v>15000</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>43709</v>
-      </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+        <v>44713</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>43983</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>45078</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -1854,34 +1878,42 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brussels Capital</t>
+          <t>Brandenburg</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>audi</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+          <t>microvast gmbh</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>1.5</v>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" s="2" t="n">
+        <v>44228</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -1889,42 +1921,42 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Budapest</t>
+          <t>Brandenburg</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>module</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>samsung sdi</t>
+          <t>oxford pv</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>42583</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" s="2" t="n">
+        <v>45536</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -1932,38 +1964,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Catalonia</t>
+          <t>Brandenburg</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>seat</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>100000</v>
-      </c>
+          <t>svolt</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" s="2" t="n">
-        <v>45748</v>
-      </c>
+      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -1971,12 +1999,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Brandenburg</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1991,7 +2019,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>eve energy</t>
+          <t>tesla</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2000,10 +2028,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45352</v>
+        <v>44197</v>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
@@ -2014,12 +2042,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Brandenburg</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2027,10 +2055,14 @@
           <t>vehicle</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>levc</t>
+          <t>tesla</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2039,12 +2071,16 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>24000</v>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+        <v>500000</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>43800</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>44256</v>
+      </c>
       <c r="K40" s="2" t="n">
-        <v>42917</v>
+        <v>44621</v>
       </c>
     </row>
     <row r="41">
@@ -2053,23 +2089,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Bratislava Region</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>red sun group</t>
+          <t>inobat</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2078,10 +2118,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>300000</v>
+        <v>10</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>43252</v>
+        <v>44105</v>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
@@ -2092,42 +2132,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Bratislava Region</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>module_pack</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>uk battery industrialisation centre</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="I42" t="inlineStr"/>
+        <v>200000</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>43709</v>
+      </c>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" s="2" t="n">
-        <v>44228</v>
-      </c>
+      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -2135,40 +2171,32 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Brussels Capital</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>volklec</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>45717</v>
-      </c>
+          <t>audi</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
     </row>
@@ -2178,12 +2206,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Budapest</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2193,12 +2221,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>west midlands gigafactory</t>
+          <t>samsung sdi</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2207,10 +2235,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>60</v>
+        <v>2.5</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>44470</v>
+        <v>42583</v>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -2221,12 +2249,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Csongrád</t>
+          <t>Catalonia</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2234,29 +2262,25 @@
           <t>vehicle</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>electric</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>build your dreams</t>
+          <t>seat</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>200000</v>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>45261</v>
-      </c>
+        <v>100000</v>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" s="2" t="n">
+        <v>45748</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -2264,12 +2288,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dundee City</t>
+          <t>City state Bremen</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2279,12 +2303,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>amte power</t>
+          <t>redux recycling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -2299,12 +2323,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Extremadura</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2319,7 +2343,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>aesc</t>
+          <t>eve energy</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2328,10 +2352,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>44652</v>
+        <v>45352</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -2342,42 +2366,38 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fejér</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>sk innovation</t>
+          <t>levc</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>10</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>44197</v>
-      </c>
+        <v>24000</v>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" s="2" t="n">
+        <v>42917</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -2385,28 +2405,36 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Flanders</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>volvo cars</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+          <t>red sun group</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>300000</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>43252</v>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
     </row>
@@ -2416,30 +2444,42 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Flanders</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>module_pack</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>volvo cars</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+          <t>uk battery industrialisation centre</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>0.0025</v>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" s="2" t="n">
+        <v>44228</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -2447,12 +2487,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Galați County</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2467,7 +2507,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>avesta battery and energy engineering</t>
+          <t>volklec</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2476,10 +2516,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>22</v>
+        <v>0.1</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45078</v>
+        <v>45717</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
@@ -2490,28 +2530,40 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Grand Est</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>psa</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
+          <t>west midlands gigafactory</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>60</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>44470</v>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
     </row>
@@ -2521,12 +2573,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Greater London</t>
+          <t>Csongrád</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2541,12 +2593,20 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>levc</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+          <t>build your dreams</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45261</v>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
     </row>
@@ -2556,12 +2616,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Greater Poland</t>
+          <t>Dundee City</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2571,12 +2631,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>johnson matthey</t>
+          <t>amte power</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -2591,28 +2651,40 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Győr-Moson-Sopron</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>audi</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
+          <t>aesc</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>50</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>44652</v>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
     </row>
@@ -2622,44 +2694,42 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hajdú-Bihar</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>deployment</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>plenitude</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>43282</v>
-      </c>
-      <c r="J56" s="2" t="n">
-        <v>44713</v>
-      </c>
-      <c r="K56" t="inlineStr"/>
+        <v>130</v>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" s="2" t="n">
+        <v>45809</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -2672,7 +2742,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hajdú-Bihar</t>
+          <t>Fejér</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2687,23 +2757,21 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>catl</t>
+          <t>sk innovation</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>44774</v>
-      </c>
-      <c r="J57" s="2" t="n">
-        <v>45778</v>
-      </c>
+        <v>44197</v>
+      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
@@ -2712,12 +2780,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hajdú-Bihar</t>
+          <t>Flanders</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2727,28 +2795,18 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ecopro bm</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H58" t="n">
-        <v>108</v>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>44531</v>
-      </c>
-      <c r="J58" s="2" t="n">
-        <v>45017</v>
-      </c>
+          <t>umicore</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
@@ -2757,12 +2815,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hajdú-Bihar</t>
+          <t>Flanders</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2770,30 +2828,16 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>eve energy</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H59" t="n">
-        <v>28</v>
-      </c>
-      <c r="I59" s="2" t="n">
-        <v>44774</v>
-      </c>
-      <c r="J59" s="2" t="n">
-        <v>45200</v>
-      </c>
+          <t>volvo cars</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
@@ -2802,38 +2846,30 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Flanders</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>hydrogen</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>h tec systems</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H60" t="n">
-        <v>1</v>
-      </c>
+          <t>volvo cars</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" s="2" t="n">
-        <v>45505</v>
-      </c>
+      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -2841,12 +2877,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Galați County</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2861,12 +2897,20 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ilika</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
+          <t>avesta battery and energy engineering</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>22</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45078</v>
+      </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
     </row>
@@ -2881,38 +2925,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Grand Est</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>aesc</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H62" t="n">
-        <v>30</v>
-      </c>
-      <c r="I62" s="2" t="n">
-        <v>44348</v>
-      </c>
-      <c r="J62" s="2" t="n">
-        <v>45231</v>
-      </c>
+          <t>psa</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
@@ -2921,43 +2951,33 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Greater London</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H63" t="n">
-        <v>13</v>
-      </c>
-      <c r="I63" s="2" t="n">
-        <v>44287</v>
-      </c>
-      <c r="J63" s="2" t="n">
-        <v>45047</v>
-      </c>
+          <t>levc</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
@@ -2966,12 +2986,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Greater Poland</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2981,28 +3001,18 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H64" t="n">
-        <v>13</v>
-      </c>
-      <c r="I64" s="2" t="n">
-        <v>44287</v>
-      </c>
-      <c r="J64" s="2" t="n">
-        <v>45047</v>
-      </c>
+          <t>johnson matthey</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -3011,42 +3021,30 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Győr-Moson-Sopron</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>automotive energy supply company</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H65" t="n">
-        <v>10</v>
-      </c>
+          <t>audi</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" s="2" t="n">
-        <v>45809</v>
-      </c>
+      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -3054,42 +3052,44 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hajdú-Bihar</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>automotive energy supply company</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>10</v>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" s="2" t="n">
-        <v>45809</v>
-      </c>
+        <v>150000</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>43282</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>44713</v>
+      </c>
+      <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -3097,41 +3097,43 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hajdú-Bihar</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>byd</t>
+          <t>catl</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>42795</v>
-      </c>
-      <c r="J67" t="inlineStr"/>
+        <v>44774</v>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>45778</v>
+      </c>
       <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
@@ -3140,12 +3142,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hajdú-Bihar</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3160,21 +3162,23 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>li cycle</t>
+          <t>ecopro bm</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>10</v>
+        <v>108</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>44986</v>
-      </c>
-      <c r="J68" t="inlineStr"/>
+        <v>44531</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>45017</v>
+      </c>
       <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
@@ -3183,12 +3187,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hajdú-Bihar</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3203,19 +3207,23 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>prologium</t>
+          <t>eve energy</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>28</v>
+      </c>
       <c r="I69" s="2" t="n">
-        <v>45078</v>
-      </c>
-      <c r="J69" t="inlineStr"/>
+        <v>44774</v>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>45200</v>
+      </c>
       <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
@@ -3224,12 +3232,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3239,19 +3247,27 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>renault</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+          <t>emr</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>10000</v>
+      </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" s="2" t="n">
+        <v>45139</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -3259,34 +3275,38 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>electric</t>
-        </is>
-      </c>
+          <t>hydrogen</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>renault</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+          <t>h tec systems</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>1</v>
+      </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" s="2" t="n">
+        <v>45505</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -3294,12 +3314,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3307,23 +3327,19 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>renault group</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H72" t="n">
-        <v>9</v>
-      </c>
-      <c r="I72" s="2" t="n">
-        <v>44440</v>
-      </c>
+          <t>ilika</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
     </row>
@@ -3348,26 +3364,28 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>renault minth</t>
+          <t>aesc</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>44713</v>
-      </c>
-      <c r="J73" t="inlineStr"/>
+        <v>44348</v>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>45231</v>
+      </c>
       <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
@@ -3396,13 +3414,23 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>saft</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+          <t>automotive cell company</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>13</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>44287</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>45047</v>
+      </c>
       <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
@@ -3421,19 +3449,33 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>module_pack</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>toyota motor europe</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+          <t>automotive cell company</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>13</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>44287</v>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>45047</v>
+      </c>
       <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
@@ -3462,24 +3504,22 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>verkor</t>
+          <t>automotive energy supply company</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>16</v>
-      </c>
-      <c r="I76" s="2" t="n">
-        <v>44593</v>
-      </c>
-      <c r="J76" s="2" t="n">
-        <v>45200</v>
-      </c>
-      <c r="K76" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" s="2" t="n">
+        <v>45809</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -3487,12 +3527,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hesse</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3507,7 +3547,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>akasol</t>
+          <t>automotive energy supply company</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3516,12 +3556,12 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" s="2" t="n">
-        <v>43191</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="78">
@@ -3530,12 +3570,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Knowsley</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3543,15 +3583,27 @@
           <t>vehicle</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ford</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
+          <t>byd</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>200</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>42795</v>
+      </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
     </row>
@@ -3561,46 +3613,42 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Komárom-Esztergom</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>byd</t>
+          <t>eramet suez</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>400</v>
+        <v>50000</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>42644</v>
-      </c>
-      <c r="J79" s="2" t="n">
-        <v>42552</v>
-      </c>
-      <c r="K79" s="2" t="n">
-        <v>42826</v>
-      </c>
+        <v>45231</v>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -3608,12 +3656,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Komárom-Esztergom</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3628,7 +3676,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>huayou cobalt</t>
+          <t>li cycle</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3637,10 +3685,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>45078</v>
+        <v>44986</v>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
@@ -3651,12 +3699,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Komárom-Esztergom</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3671,26 +3719,20 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>sk innovation</t>
+          <t>prologium</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H81" t="n">
-        <v>7.5</v>
-      </c>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" s="2" t="n">
-        <v>43040</v>
-      </c>
-      <c r="J81" s="2" t="n">
-        <v>43160</v>
-      </c>
-      <c r="K81" s="2" t="n">
-        <v>44197</v>
-      </c>
+        <v>45078</v>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -3698,40 +3740,32 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Košice Region</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>volvo cars</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H82" t="n">
-        <v>250000</v>
-      </c>
-      <c r="I82" s="2" t="n">
-        <v>44743</v>
-      </c>
+          <t>renault</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
     </row>
@@ -3741,12 +3775,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Košice Region</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3761,20 +3795,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>zhi dou</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H83" t="n">
-        <v>60000</v>
-      </c>
-      <c r="I83" s="2" t="n">
-        <v>43191</v>
-      </c>
+          <t>renault</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
     </row>
@@ -3784,12 +3810,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kymenlaakso</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3797,28 +3823,24 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>eam</t>
-        </is>
-      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>easpring finland new materials oy</t>
+          <t>renault group</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>60</v>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" s="2" t="n">
-        <v>45717</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>44440</v>
+      </c>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
@@ -3827,12 +3849,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Kymenlaakso</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3847,7 +3869,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>finnish minerals beijing easpring</t>
+          <t>renault minth</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3856,10 +3878,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>37.5</v>
+        <v>15</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>45139</v>
+        <v>44713</v>
       </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
@@ -3870,12 +3892,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kymenlaakso</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3890,20 +3912,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>finnish minerals group</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H86" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="I86" s="2" t="n">
-        <v>45139</v>
-      </c>
+          <t>saft</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
     </row>
@@ -3913,42 +3927,30 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>solar</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>deployment</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>baywa re</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H87" t="n">
-        <v>9</v>
-      </c>
+          <t>toyota motor europe</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
-      <c r="K87" s="2" t="n">
-        <v>45566</v>
-      </c>
+      <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -3956,29 +3958,43 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>lotus</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
+          <t>verkor</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>16</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>44593</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>45200</v>
+      </c>
       <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
@@ -3992,7 +4008,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Hesse</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4002,27 +4018,27 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>gotion high tech</t>
+          <t>akasol</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I89" s="2" t="n">
-        <v>44409</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" s="2" t="n">
+        <v>43191</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -4030,12 +4046,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4045,12 +4061,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>gotion high tech</t>
+          <t>glencore britishvolt</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4059,10 +4075,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>3.5</v>
+        <v>10000</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>44409</v>
+        <v>44593</v>
       </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
@@ -4073,39 +4089,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Knowsley</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>eam</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>graphenix development inc</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>under construction</t>
-        </is>
-      </c>
+          <t>ford</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" s="2" t="n">
-        <v>45292</v>
-      </c>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
@@ -4114,27 +4120,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Komárom-Esztergom</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>byd</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -4143,16 +4149,16 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>44317</v>
+        <v>42644</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>45627</v>
+        <v>42552</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>43586</v>
+        <v>42826</v>
       </c>
     </row>
     <row r="93">
@@ -4161,12 +4167,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Komárom-Esztergom</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4181,26 +4187,22 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>huayou cobalt</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>44317</v>
-      </c>
-      <c r="J93" s="2" t="n">
-        <v>45627</v>
-      </c>
-      <c r="K93" s="2" t="n">
-        <v>43586</v>
-      </c>
+        <v>45078</v>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -4208,42 +4210,46 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Komárom-Esztergom</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>sk innovation</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>300000</v>
+        <v>7.5</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>43709</v>
-      </c>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
+        <v>43040</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>43160</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>44197</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -4251,41 +4257,41 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Košice Region</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>volkswagen northvolt</t>
+          <t>volvo cars</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>16</v>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" s="2" t="n">
-        <v>43709</v>
-      </c>
+        <v>250000</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>44743</v>
+      </c>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
@@ -4294,23 +4300,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Lower Silesia</t>
+          <t>Košice Region</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr"/>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>lg chem</t>
+          <t>zhi dou</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4319,10 +4329,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>5</v>
+        <v>60000</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>42644</v>
+        <v>43191</v>
       </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
@@ -4333,12 +4343,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Lower Silesia</t>
+          <t>Kymenlaakso</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4348,27 +4358,27 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>lg energy solution</t>
+          <t>easpring finland new materials oy</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" s="2" t="n">
-        <v>45261</v>
-      </c>
+      <c r="J97" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -4376,12 +4386,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Molise</t>
+          <t>Kymenlaakso</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4391,12 +4401,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
+          <t>finnish minerals beijing easpring</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4405,10 +4415,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>45444</v>
+        <v>45139</v>
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
@@ -4419,12 +4429,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Nitra Region</t>
+          <t>Kymenlaakso</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4439,7 +4449,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>gotion inobat batteries</t>
+          <t>finnish minerals group</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4448,10 +4458,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>20</v>
+        <v>33.5</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>45231</v>
+        <v>45139</v>
       </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
@@ -4462,42 +4472,42 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Nordland</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>deployment</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>freyr</t>
+          <t>baywa re</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" s="2" t="n">
-        <v>43678</v>
-      </c>
-      <c r="J100" s="2" t="n">
-        <v>44470</v>
-      </c>
-      <c r="K100" t="inlineStr"/>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>9</v>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" s="2" t="n">
+        <v>45566</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -4505,41 +4515,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Nordland</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>eam</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>freyr</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>under construction</t>
-        </is>
-      </c>
+          <t>lotus</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
-      <c r="I101" s="2" t="n">
-        <v>43678</v>
-      </c>
-      <c r="J101" s="2" t="n">
-        <v>44470</v>
-      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
@@ -4548,12 +4546,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Normandy</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4561,23 +4559,19 @@
           <t>vehicle</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>hopium</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H102" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I102" s="2" t="n">
-        <v>44805</v>
-      </c>
+          <t>electricbrands</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
     </row>
@@ -4587,32 +4581,40 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Normandy</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>renault</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
+          <t>gotion high tech</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>44409</v>
+      </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
     </row>
@@ -4627,27 +4629,35 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>ego mobile</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
+          <t>gotion high tech</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>44409</v>
+      </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
     </row>
@@ -4662,28 +4672,34 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>ford</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr"/>
+          <t>graphenix development inc</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
+      <c r="J105" s="2" t="n">
+        <v>45292</v>
+      </c>
       <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
@@ -4697,7 +4713,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4712,20 +4728,26 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>fraunhofer ffb</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>20</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>44317</v>
+      </c>
       <c r="J106" s="2" t="n">
-        <v>45444</v>
-      </c>
-      <c r="K106" t="inlineStr"/>
+        <v>45627</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>43586</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -4738,37 +4760,41 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>nextego mobile</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>30000</v>
+        <v>20</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>45200</v>
-      </c>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
+        <v>44317</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>45627</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>43586</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -4781,18 +4807,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr"/>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>primobius</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4801,10 +4831,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>20000</v>
+        <v>300000</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>44317</v>
+        <v>43709</v>
       </c>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
@@ -4820,7 +4850,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4830,12 +4860,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>pure battery technologies</t>
+          <t>volkswagen group components</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4844,12 +4874,12 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>10</v>
+        <v>3600</v>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" s="2" t="n">
-        <v>44713</v>
+        <v>44197</v>
       </c>
     </row>
     <row r="110">
@@ -4863,7 +4893,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4871,10 +4901,14 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>rwth aachen university</t>
+          <t>volkswagen northvolt</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4882,10 +4916,12 @@
           <t>under construction</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
+      <c r="H110" t="n">
+        <v>16</v>
+      </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" s="2" t="n">
-        <v>45292</v>
+        <v>43709</v>
       </c>
       <c r="K110" t="inlineStr"/>
     </row>
@@ -4895,12 +4931,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Northumberland</t>
+          <t>Lower Silesia</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4908,30 +4944,24 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>britishvolt</t>
+          <t>lg chem</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>44197</v>
-      </c>
-      <c r="J111" s="2" t="n">
-        <v>44531</v>
-      </c>
+        <v>42644</v>
+      </c>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
@@ -4940,12 +4970,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Northumberland</t>
+          <t>Lower Silesia</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4960,24 +4990,22 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>britishvolt</t>
+          <t>lg energy solution</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>4</v>
-      </c>
-      <c r="I112" s="2" t="n">
-        <v>44197</v>
-      </c>
-      <c r="J112" s="2" t="n">
-        <v>44531</v>
-      </c>
-      <c r="K112" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" s="2" t="n">
+        <v>45261</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -4985,12 +5013,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Nouvelle-Aquitaine</t>
+          <t>Molise</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5000,27 +5028,27 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>forsee power</t>
+          <t>automotive cell company</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>1</v>
-      </c>
-      <c r="I113" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>45444</v>
+      </c>
       <c r="J113" t="inlineStr"/>
-      <c r="K113" s="2" t="n">
-        <v>44986</v>
-      </c>
+      <c r="K113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -5028,12 +5056,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Nouvelle-Aquitaine</t>
+          <t>Nitra Region</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5043,17 +5071,25 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>startec energy</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
+          <t>gotion inobat batteries</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>20</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>45231</v>
+      </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
     </row>
@@ -5063,41 +5099,41 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Novo Mesto</t>
+          <t>Nordland</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>revoz</t>
+          <t>freyr</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H115" t="n">
-        <v>150000</v>
-      </c>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" s="2" t="n">
-        <v>45474</v>
-      </c>
-      <c r="J115" t="inlineStr"/>
+        <v>43678</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>44470</v>
+      </c>
       <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
@@ -5106,41 +5142,41 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Opole Voivodeship</t>
+          <t>Nordland</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>deployment</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>ox2</t>
+          <t>freyr</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H116" t="n">
-        <v>90</v>
-      </c>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" s="2" t="n">
-        <v>45839</v>
-      </c>
-      <c r="J116" t="inlineStr"/>
+        <v>43678</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>44470</v>
+      </c>
       <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
@@ -5149,42 +5185,38 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Opole Voivodeship</t>
+          <t>Normandy</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>eam</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>umicore</t>
+          <t>hopium</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>20</v>
-      </c>
-      <c r="I117" t="inlineStr"/>
+        <v>20000</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>44805</v>
+      </c>
       <c r="J117" t="inlineStr"/>
-      <c r="K117" s="2" t="n">
-        <v>44958</v>
-      </c>
+      <c r="K117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -5192,40 +5224,32 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ostrobothnia</t>
+          <t>Normandy</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>finnish minerals group epsilon advanced materials</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H118" t="n">
-        <v>50</v>
-      </c>
-      <c r="I118" s="2" t="n">
-        <v>44866</v>
-      </c>
+          <t>renault</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
     </row>
@@ -5235,12 +5259,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ostrobothnia</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5250,27 +5274,27 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>freyr battery</t>
+          <t>cylib</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>30</v>
-      </c>
-      <c r="I119" s="2" t="n">
-        <v>45566</v>
-      </c>
+        <v>9.125</v>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" s="2" t="n">
+        <v>45261</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -5278,40 +5302,32 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ostrobothnia</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>johnson matthey</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H120" t="n">
-        <v>30</v>
-      </c>
-      <c r="I120" s="2" t="n">
-        <v>44287</v>
-      </c>
+          <t>ego mobile</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
     </row>
@@ -5321,12 +5337,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5341,7 +5357,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>ford</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
@@ -5356,41 +5372,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>deployment</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>photovolt development partners</t>
+          <t>fraunhofer ffb</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H122" t="n">
-        <v>840</v>
-      </c>
-      <c r="I122" s="2" t="n">
-        <v>45778</v>
-      </c>
-      <c r="J122" t="inlineStr"/>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" s="2" t="n">
+        <v>45444</v>
+      </c>
       <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
@@ -5399,32 +5413,40 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Pest County</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>samsung sdi</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
+          <t>nextego mobile</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>45200</v>
+      </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
     </row>
@@ -5434,42 +5456,38 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>electric</t>
-        </is>
-      </c>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>fiat chrysler</t>
+          <t>primobius</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>80000</v>
-      </c>
-      <c r="I124" t="inlineStr"/>
+        <v>20000</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>44317</v>
+      </c>
       <c r="J124" t="inlineStr"/>
-      <c r="K124" s="2" t="n">
-        <v>43862</v>
-      </c>
+      <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -5477,12 +5495,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5492,27 +5510,27 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>italvolt</t>
+          <t>pure battery technologies</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>45</v>
-      </c>
-      <c r="I125" s="2" t="n">
-        <v>44348</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" s="2" t="n">
+        <v>44713</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -5520,42 +5538,36 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>electric</t>
-        </is>
-      </c>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>micro mobility</t>
+          <t>rwth aachen university</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H126" t="n">
-        <v>7500</v>
-      </c>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" s="2" t="n">
-        <v>44440</v>
-      </c>
+      <c r="J126" s="2" t="n">
+        <v>45292</v>
+      </c>
+      <c r="K126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -5563,29 +5575,43 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>Northumberland</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>stellantis</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
+          <t>britishvolt</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>4</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>44197</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>44531</v>
+      </c>
       <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
@@ -5594,12 +5620,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Pomerania</t>
+          <t>Northumberland</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -5614,21 +5640,23 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>northvolt south bay solutions</t>
+          <t>britishvolt</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>43374</v>
-      </c>
-      <c r="J128" t="inlineStr"/>
+        <v>44197</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>44531</v>
+      </c>
       <c r="K128" t="inlineStr"/>
     </row>
     <row r="129">
@@ -5637,12 +5665,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Rheinland-Pfalz</t>
+          <t>Nouvelle-Aquitaine</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -5652,29 +5680,27 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
+          <t>forsee power</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>8</v>
-      </c>
-      <c r="I129" s="2" t="n">
-        <v>43862</v>
-      </c>
-      <c r="J129" s="2" t="n">
-        <v>44440</v>
-      </c>
-      <c r="K129" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" s="2" t="n">
+        <v>44986</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -5682,12 +5708,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Rheinland-Pfalz</t>
+          <t>Nouvelle-Aquitaine</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -5702,23 +5728,13 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H130" t="n">
-        <v>8</v>
-      </c>
-      <c r="I130" s="2" t="n">
-        <v>43862</v>
-      </c>
-      <c r="J130" s="2" t="n">
-        <v>44440</v>
-      </c>
+          <t>startec energy</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
@@ -5727,38 +5743,42 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Rheinland-Pfalz</t>
+          <t>Novo Mesto</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr"/>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>e lyte</t>
+          <t>revoz</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I131" t="inlineStr"/>
+        <v>150000</v>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>45474</v>
+      </c>
       <c r="J131" t="inlineStr"/>
-      <c r="K131" s="2" t="n">
-        <v>45536</v>
-      </c>
+      <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -5766,37 +5786,41 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ruse</t>
+          <t>Opole Voivodeship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>eberspacher</t>
+          <t>ox2</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" s="2" t="n">
-        <v>45017</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
     </row>
     <row r="133">
@@ -5805,12 +5829,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Saarland</t>
+          <t>Opole Voivodeship</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -5820,29 +5844,27 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>svolt</t>
+          <t>umicore</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>297</v>
-      </c>
-      <c r="I133" s="2" t="n">
-        <v>44136</v>
-      </c>
-      <c r="J133" s="2" t="n">
-        <v>44531</v>
-      </c>
-      <c r="K133" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" s="2" t="n">
+        <v>44958</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -5855,7 +5877,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Satakunta</t>
+          <t>Ostrobothnia</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -5870,23 +5892,21 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>basf</t>
+          <t>finnish minerals group epsilon advanced materials</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>43405</v>
-      </c>
-      <c r="J134" s="2" t="n">
-        <v>43983</v>
-      </c>
+        <v>44866</v>
+      </c>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
@@ -5895,12 +5915,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Ostrobothnia</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -5910,31 +5930,27 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>blackstone technology</t>
+          <t>freyr battery</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>0.5</v>
+        <v>30</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>44228</v>
-      </c>
-      <c r="J135" s="2" t="n">
-        <v>44440</v>
-      </c>
-      <c r="K135" s="2" t="n">
-        <v>43466</v>
-      </c>
+        <v>45566</v>
+      </c>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -5942,12 +5958,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Ostrobothnia</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -5957,17 +5973,25 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>bmw</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
+          <t>johnson matthey</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>30</v>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>44287</v>
+      </c>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
     </row>
@@ -5977,12 +6001,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6012,12 +6036,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6027,12 +6051,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>ingot_wafer</t>
+          <t>deployment</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>european semiconductor manufacturing company</t>
+          <t>photovolt development partners</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -6041,10 +6065,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>480000</v>
+        <v>840</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>45627</v>
+        <v>45778</v>
       </c>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
@@ -6055,12 +6079,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Pest County</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6070,12 +6094,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>jt energy systems</t>
+          <t>samsung sdi</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
@@ -6090,34 +6114,42 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Piedmont</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>meyer burger</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
+          <t>fiat chrysler</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>80000</v>
+      </c>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" s="2" t="n">
+        <v>43862</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -6125,12 +6157,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Piedmont</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6138,10 +6170,14 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>porsche</t>
+          <t>italvolt</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -6150,10 +6186,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>45566</v>
+        <v>44348</v>
       </c>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
@@ -6164,12 +6200,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Piedmont</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6184,22 +6220,22 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>micro mobility</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>109500</v>
-      </c>
-      <c r="I142" s="2" t="n">
-        <v>42856</v>
-      </c>
+        <v>7500</v>
+      </c>
+      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" s="2" t="n">
+        <v>44440</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -6207,41 +6243,29 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Piedmont</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>eam</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>amg lithium</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H143" t="n">
-        <v>20</v>
-      </c>
+          <t>stellantis</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" s="2" t="n">
-        <v>45047</v>
-      </c>
+      <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
     </row>
     <row r="144">
@@ -6250,12 +6274,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Pirkanmaa</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -6263,25 +6287,29 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>recycling</t>
+        </is>
+      </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>battery lifecycle company</t>
+          <t>fortum</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>15000</v>
-      </c>
-      <c r="I144" t="inlineStr"/>
+        <v>3000</v>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>44197</v>
+      </c>
       <c r="J144" t="inlineStr"/>
-      <c r="K144" s="2" t="n">
-        <v>45505</v>
-      </c>
+      <c r="K144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -6289,12 +6317,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Pirkanmaa</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -6304,25 +6332,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>farasis energy</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H145" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I145" s="2" t="n">
-        <v>44228</v>
-      </c>
+          <t>fortum battery recycling</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
     </row>
@@ -6332,12 +6352,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Pomerania</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -6347,17 +6367,25 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>farasis energy europe</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
+          <t>northvolt south bay solutions</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>43374</v>
+      </c>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
     </row>
@@ -6372,7 +6400,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Schleswig-Holstein</t>
+          <t>Rheinland-Pfalz</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -6387,7 +6415,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>northvolt</t>
+          <t>automotive cell company</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -6396,13 +6424,13 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>44621</v>
+        <v>43862</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>45352</v>
+        <v>44440</v>
       </c>
       <c r="K147" t="inlineStr"/>
     </row>
@@ -6412,12 +6440,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Schwyz</t>
+          <t>Rheinland-Pfalz</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -6425,10 +6453,14 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>module_pack</t>
+        </is>
+      </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>ecovolta</t>
+          <t>automotive cell company</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -6437,11 +6469,13 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I148" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>43862</v>
+      </c>
       <c r="J148" s="2" t="n">
-        <v>43252</v>
+        <v>44440</v>
       </c>
       <c r="K148" t="inlineStr"/>
     </row>
@@ -6451,12 +6485,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Rheinland-Pfalz</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -6464,29 +6498,25 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>calb</t>
+          <t>e lyte</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>15</v>
-      </c>
-      <c r="I149" s="2" t="n">
-        <v>44866</v>
-      </c>
+        <v>20000</v>
+      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" s="2" t="n">
+        <v>45536</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -6494,23 +6524,27 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr"/>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>sng solar</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -6519,10 +6553,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>100000</v>
+        <v>100</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>45748</v>
+        <v>45839</v>
       </c>
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
@@ -6533,12 +6567,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Silesia</t>
+          <t>Ruse</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -6549,21 +6583,21 @@
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>eberspacher</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I151" s="2" t="n">
-        <v>44958</v>
-      </c>
-      <c r="J151" t="inlineStr"/>
+        <v>2400000</v>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" s="2" t="n">
+        <v>45017</v>
+      </c>
       <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
@@ -6572,12 +6606,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Saarland</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -6592,7 +6626,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>agratas</t>
+          <t>svolt</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -6601,13 +6635,13 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>40</v>
+        <v>297</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>45108</v>
+        <v>44136</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>45689</v>
+        <v>44531</v>
       </c>
       <c r="K152" t="inlineStr"/>
     </row>
@@ -6617,12 +6651,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Southwest Finland</t>
+          <t>Sardinia</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -6632,17 +6666,25 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>valmet automotive</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
+          <t>li cycle glencore</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>45139</v>
+      </c>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
     </row>
@@ -6657,32 +6699,38 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Southwest Finland</t>
+          <t>Satakunta</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>eam</t>
+        </is>
+      </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>valmet automotive</t>
+          <t>basf</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H154" t="n">
-        <v>257000</v>
+        <v>20</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>44652</v>
-      </c>
-      <c r="J154" t="inlineStr"/>
+        <v>43405</v>
+      </c>
+      <c r="J154" s="2" t="n">
+        <v>43983</v>
+      </c>
       <c r="K154" t="inlineStr"/>
     </row>
     <row r="155">
@@ -6696,29 +6744,41 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>State of Berlin</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>tesla</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
+          <t>blackstone technology</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>44228</v>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>44440</v>
+      </c>
+      <c r="K155" s="2" t="n">
+        <v>43466</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -6726,12 +6786,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -6741,31 +6801,19 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>aesc</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H156" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I156" s="2" t="n">
-        <v>44317</v>
-      </c>
-      <c r="J156" s="2" t="n">
-        <v>44470</v>
-      </c>
-      <c r="K156" s="2" t="n">
-        <v>45292</v>
-      </c>
+          <t>bmw</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -6773,46 +6821,34 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>aesc</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H157" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I157" s="2" t="n">
-        <v>44317</v>
-      </c>
-      <c r="J157" s="2" t="n">
-        <v>44470</v>
-      </c>
-      <c r="K157" s="2" t="n">
-        <v>45292</v>
-      </c>
+          <t>bmw</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -6820,43 +6856,41 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>ingot_wafer</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>nissan</t>
+          <t>european semiconductor manufacturing company</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H158" t="n">
-        <v>35</v>
+        <v>480000</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>44896</v>
-      </c>
-      <c r="J158" s="2" t="n">
-        <v>45231</v>
-      </c>
+        <v>45627</v>
+      </c>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
     </row>
     <row r="159">
@@ -6865,41 +6899,33 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>nissan</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>under construction</t>
-        </is>
-      </c>
+          <t>jt energy systems</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr"/>
-      <c r="I159" s="2" t="n">
-        <v>44378</v>
-      </c>
-      <c r="J159" s="2" t="n">
-        <v>45352</v>
-      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
     </row>
     <row r="160">
@@ -6908,23 +6934,27 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr"/>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>saietta group</t>
+          <t>meyer burger</t>
         </is>
       </c>
       <c r="G160" t="inlineStr"/>
@@ -6939,12 +6969,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Telemark</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -6952,29 +6982,25 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>eam</t>
-        </is>
-      </c>
+      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>vianode</t>
+          <t>porsche</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H161" t="n">
-        <v>2</v>
-      </c>
-      <c r="I161" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="I161" s="2" t="n">
+        <v>45566</v>
+      </c>
       <c r="J161" t="inlineStr"/>
-      <c r="K161" s="2" t="n">
-        <v>45566</v>
-      </c>
+      <c r="K161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -6987,39 +7013,37 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Thuringia</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>catl</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H162" t="n">
-        <v>8</v>
+        <v>109500</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>43282</v>
+        <v>42856</v>
       </c>
       <c r="J162" t="inlineStr"/>
-      <c r="K162" s="2" t="n">
-        <v>44501</v>
-      </c>
+      <c r="K162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -7032,7 +7056,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Thuringia</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -7042,12 +7066,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>lion smart</t>
+          <t>amg lithium</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -7056,11 +7080,11 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>240</v>
+        <v>20</v>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="J163" s="2" t="n">
-        <v>45139</v>
+        <v>45047</v>
       </c>
       <c r="K163" t="inlineStr"/>
     </row>
@@ -7070,12 +7094,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Trnava Region</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -7083,29 +7107,25 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
+      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>gotion inobat batteries</t>
+          <t>battery lifecycle company</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H164" t="n">
-        <v>20</v>
-      </c>
-      <c r="I164" s="2" t="n">
-        <v>45261</v>
-      </c>
+        <v>15000</v>
+      </c>
+      <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" s="2" t="n">
+        <v>45505</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -7113,12 +7133,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Trnava Region</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -7133,26 +7153,22 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>inobat</t>
+          <t>farasis energy</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H165" t="n">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>44105</v>
-      </c>
-      <c r="J165" s="2" t="n">
-        <v>44317</v>
-      </c>
-      <c r="K165" s="2" t="n">
-        <v>45261</v>
-      </c>
+        <v>44228</v>
+      </c>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -7160,12 +7176,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Trnava Region</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -7175,31 +7191,19 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>inobat</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H166" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I166" s="2" t="n">
-        <v>44105</v>
-      </c>
-      <c r="J166" s="2" t="n">
-        <v>44317</v>
-      </c>
-      <c r="K166" s="2" t="n">
-        <v>45261</v>
-      </c>
+          <t>farasis energy europe</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -7207,12 +7211,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Trøndelag</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -7222,25 +7226,29 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>elinor batteries</t>
+          <t>li cycle</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" s="2" t="n">
-        <v>44927</v>
-      </c>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H167" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" s="2" t="n">
+        <v>44986</v>
+      </c>
+      <c r="K167" s="2" t="n">
+        <v>45139</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -7248,23 +7256,27 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Utena</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>solar</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>eam</t>
+        </is>
+      </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>european energy</t>
+          <t>norcsi</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -7272,12 +7284,10 @@
           <t>under construction</t>
         </is>
       </c>
-      <c r="H168" t="n">
-        <v>78.5</v>
-      </c>
+      <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
       <c r="J168" s="2" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="K168" t="inlineStr"/>
     </row>
@@ -7287,12 +7297,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Schleswig-Holstein</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -7307,7 +7317,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>northvolt</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -7316,13 +7326,13 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="J169" s="2" t="n">
-        <v>45566</v>
+        <v>45352</v>
       </c>
       <c r="K169" t="inlineStr"/>
     </row>
@@ -7332,12 +7342,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Schwyz</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -7345,14 +7355,10 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>eam</t>
-        </is>
-      </c>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>ecovolta</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -7361,13 +7367,11 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>40</v>
-      </c>
-      <c r="I170" s="2" t="n">
-        <v>44593</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="I170" t="inlineStr"/>
       <c r="J170" s="2" t="n">
-        <v>45566</v>
+        <v>43252</v>
       </c>
       <c r="K170" t="inlineStr"/>
     </row>
@@ -7377,27 +7381,27 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>calb</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -7406,10 +7410,10 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>44927</v>
+        <v>44866</v>
       </c>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
@@ -7420,37 +7424,41 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Vas County</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>module_pack</t>
+        </is>
+      </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>schaeffler</t>
+          <t>calb</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H172" t="n">
-        <v>800000</v>
-      </c>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" s="2" t="n">
-        <v>44440</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>44866</v>
+      </c>
+      <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
@@ -7464,7 +7472,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Viseu</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -7472,19 +7480,23 @@
           <t>vehicle</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>electric</t>
-        </is>
-      </c>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>stellantis</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
+          <t>volkswagen</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H173" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>45748</v>
+      </c>
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr"/>
     </row>
@@ -7494,27 +7506,27 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Warwickshire</t>
+          <t>Silesia</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>london taxi company</t>
+          <t>ae elemental</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -7523,12 +7535,14 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I174" t="inlineStr"/>
+        <v>12000</v>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>45383</v>
+      </c>
       <c r="J174" t="inlineStr"/>
       <c r="K174" s="2" t="n">
-        <v>42795</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="175">
@@ -7537,38 +7551,38 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Silesia</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>battrion</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H175" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I175" t="inlineStr"/>
+        <v>10000</v>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>44958</v>
+      </c>
       <c r="J175" t="inlineStr"/>
-      <c r="K175" s="2" t="n">
-        <v>44287</v>
-      </c>
+      <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
@@ -7576,12 +7590,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Świętokrzyskie</t>
+          <t>Solothurn</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -7591,12 +7605,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>green cell</t>
+          <t>librec</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -7605,11 +7619,1275 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>2.5</v>
+        <v>12000</v>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
       <c r="K176" s="2" t="n">
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>175</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Somerset</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>agratas</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H177" t="n">
+        <v>40</v>
+      </c>
+      <c r="I177" s="2" t="n">
+        <v>45108</v>
+      </c>
+      <c r="J177" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="K177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>176</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Southwest Finland</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>module_pack</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>valmet automotive</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>177</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Southwest Finland</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>valmet automotive</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H179" t="n">
+        <v>257000</v>
+      </c>
+      <c r="I179" s="2" t="n">
+        <v>44652</v>
+      </c>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>178</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>State of Berlin</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>tesla</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>179</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>aesc</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H181" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I181" s="2" t="n">
+        <v>44317</v>
+      </c>
+      <c r="J181" s="2" t="n">
+        <v>44470</v>
+      </c>
+      <c r="K181" s="2" t="n">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>module_pack</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>aesc</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H182" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>44317</v>
+      </c>
+      <c r="J182" s="2" t="n">
+        <v>44470</v>
+      </c>
+      <c r="K182" s="2" t="n">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>181</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>nissan</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H183" t="n">
+        <v>35</v>
+      </c>
+      <c r="I183" s="2" t="n">
+        <v>44896</v>
+      </c>
+      <c r="J183" s="2" t="n">
+        <v>45231</v>
+      </c>
+      <c r="K183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>182</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>nissan</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" s="2" t="n">
+        <v>44378</v>
+      </c>
+      <c r="J184" s="2" t="n">
+        <v>45352</v>
+      </c>
+      <c r="K184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>183</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>saietta group</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>184</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Telemark</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>eam</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>vianode</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H186" t="n">
+        <v>2</v>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" s="2" t="n">
+        <v>45566</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>185</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Thuringia</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>catl</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H187" t="n">
+        <v>8</v>
+      </c>
+      <c r="I187" s="2" t="n">
+        <v>43282</v>
+      </c>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" s="2" t="n">
+        <v>44501</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>186</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Thuringia</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>module_pack</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>lion smart</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H188" t="n">
+        <v>240</v>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" s="2" t="n">
+        <v>45139</v>
+      </c>
+      <c r="K188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>187</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Thuringia</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>recycling</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>sungeel hitech and samsung</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H189" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I189" s="2" t="n">
+        <v>45170</v>
+      </c>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>188</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Trnava Region</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>gotion inobat batteries</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H190" t="n">
+        <v>20</v>
+      </c>
+      <c r="I190" s="2" t="n">
+        <v>45261</v>
+      </c>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>189</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Trnava Region</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>inobat</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H191" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I191" s="2" t="n">
+        <v>44105</v>
+      </c>
+      <c r="J191" s="2" t="n">
+        <v>44317</v>
+      </c>
+      <c r="K191" s="2" t="n">
+        <v>45261</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Trnava Region</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>module_pack</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>inobat</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H192" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I192" s="2" t="n">
+        <v>44105</v>
+      </c>
+      <c r="J192" s="2" t="n">
+        <v>44317</v>
+      </c>
+      <c r="K192" s="2" t="n">
+        <v>45261</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>191</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Trøndelag</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>elinor batteries</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" s="2" t="n">
+        <v>44927</v>
+      </c>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>192</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Tukums Municipality</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>ignitis renewables</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H194" t="n">
+        <v>174</v>
+      </c>
+      <c r="I194" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>193</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Utena</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>european energy</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H195" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="K195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>194</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>volkswagen</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H196" t="n">
+        <v>40</v>
+      </c>
+      <c r="I196" s="2" t="n">
+        <v>44593</v>
+      </c>
+      <c r="J196" s="2" t="n">
+        <v>45566</v>
+      </c>
+      <c r="K196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>195</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>eam</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>volkswagen</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H197" t="n">
+        <v>40</v>
+      </c>
+      <c r="I197" s="2" t="n">
+        <v>44593</v>
+      </c>
+      <c r="J197" s="2" t="n">
+        <v>45566</v>
+      </c>
+      <c r="K197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>196</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>volkswagen</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H198" t="n">
+        <v>40</v>
+      </c>
+      <c r="I198" s="2" t="n">
+        <v>44927</v>
+      </c>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>197</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Vas County</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>schaeffler</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H199" t="n">
+        <v>800000</v>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" s="2" t="n">
+        <v>44440</v>
+      </c>
+      <c r="K199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>198</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Viseu</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>stellantis</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>199</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Warwickshire</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>london taxi company</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H201" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" s="2" t="n">
+        <v>42795</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Wolverhampton</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>recycling</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>recyclus group</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H202" t="n">
+        <v>22000</v>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" s="2" t="n">
+        <v>45200</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>201</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>battrion</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H203" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" s="2" t="n">
+        <v>44287</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>202</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Île-de-France</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>recycling</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>lg energy solution derichebourg</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H204" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I204" s="2" t="n">
+        <v>45748</v>
+      </c>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>203</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Østfold</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>recycling</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>hydrovolt</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H205" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" s="2" t="n">
+        <v>44228</v>
+      </c>
+      <c r="K205" s="2" t="n">
+        <v>44228</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>204</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Świętokrzyskie</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>module_pack</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>green cell</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H206" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" s="2" t="n">
         <v>44652</v>
       </c>
     </row>

--- a/reconcile/storage/output/capacities_plot.xlsx
+++ b/reconcile/storage/output/capacities_plot.xlsx
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>9.125</v>
+        <v>9125</v>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>

--- a/reconcile/storage/output/capacities_plot.xlsx
+++ b/reconcile/storage/output/capacities_plot.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K206"/>
+  <dimension ref="A1:K204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>263</v>
+        <v>0.263</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>50</v>
+        <v>0.05</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>145</v>
+        <v>0.145</v>
       </c>
       <c r="I21" s="2" t="n">
         <v>45839</v>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>14</v>
+        <v>0.014</v>
       </c>
       <c r="I29" s="2" t="n">
         <v>45566</v>
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>100</v>
+        <v>0.1</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>130</v>
+        <v>0.13</v>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>108</v>
+        <v>108000</v>
       </c>
       <c r="I68" s="2" t="n">
         <v>44531</v>
@@ -3275,38 +3275,34 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>hydrogen</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>h tec systems</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H71" t="n">
-        <v>1</v>
-      </c>
+          <t>ilika</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
-      <c r="K71" s="2" t="n">
-        <v>45505</v>
-      </c>
+      <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -3314,12 +3310,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3334,13 +3330,23 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ilika</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+          <t>aesc</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>30</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>44348</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>45231</v>
+      </c>
       <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
@@ -3369,7 +3375,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>aesc</t>
+          <t>automotive cell company</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3378,13 +3384,13 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>44348</v>
+        <v>44287</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>45231</v>
+        <v>45047</v>
       </c>
       <c r="K73" t="inlineStr"/>
     </row>
@@ -3409,7 +3415,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3454,29 +3460,27 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
+          <t>automotive energy supply company</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>13</v>
-      </c>
-      <c r="I75" s="2" t="n">
-        <v>44287</v>
-      </c>
-      <c r="J75" s="2" t="n">
-        <v>45047</v>
-      </c>
-      <c r="K75" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" s="2" t="n">
+        <v>45809</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -3499,7 +3503,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3537,32 +3541,32 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>automotive energy supply company</t>
+          <t>byd</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>10</v>
-      </c>
-      <c r="I77" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>42795</v>
+      </c>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" s="2" t="n">
-        <v>45809</v>
-      </c>
+      <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -3580,17 +3584,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>byd</t>
+          <t>eramet suez</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3599,10 +3603,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>200</v>
+        <v>50000</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>42795</v>
+        <v>45231</v>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
@@ -3628,12 +3632,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>recycling</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>eramet suez</t>
+          <t>li cycle</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3642,10 +3646,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>45231</v>
+        <v>44986</v>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
@@ -3671,12 +3675,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>li cycle</t>
+          <t>prologium</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3684,11 +3688,9 @@
           <t>announced</t>
         </is>
       </c>
-      <c r="H80" t="n">
-        <v>10</v>
-      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" s="2" t="n">
-        <v>44986</v>
+        <v>45078</v>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
@@ -3719,18 +3721,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>prologium</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
+          <t>renault</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
-      <c r="I81" s="2" t="n">
-        <v>45078</v>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
     </row>
@@ -3750,12 +3746,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3785,22 +3781,26 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>electric</t>
-        </is>
-      </c>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>renault</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
+          <t>renault group</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>9</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>44440</v>
+      </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
     </row>
@@ -3823,10 +3823,14 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>eam</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>renault group</t>
+          <t>renault minth</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3835,10 +3839,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>44440</v>
+        <v>44713</v>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
@@ -3864,25 +3868,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>renault minth</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H85" t="n">
-        <v>15</v>
-      </c>
-      <c r="I85" s="2" t="n">
-        <v>44713</v>
-      </c>
+          <t>saft</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
     </row>
@@ -3902,17 +3898,13 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>saft</t>
+          <t>toyota motor europe</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -3937,19 +3929,33 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>toyota motor europe</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
+          <t>verkor</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>16</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>44593</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>45200</v>
+      </c>
       <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
@@ -3958,12 +3964,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hesse</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3973,29 +3979,27 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>verkor</t>
+          <t>akasol</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>16</v>
-      </c>
-      <c r="I88" s="2" t="n">
-        <v>44593</v>
-      </c>
-      <c r="J88" s="2" t="n">
-        <v>45200</v>
-      </c>
-      <c r="K88" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" s="2" t="n">
+        <v>43191</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -4003,12 +4007,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Hesse</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4018,27 +4022,27 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>akasol</t>
+          <t>glencore britishvolt</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
-      </c>
-      <c r="I89" t="inlineStr"/>
+        <v>10000</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>44593</v>
+      </c>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" s="2" t="n">
-        <v>43191</v>
-      </c>
+      <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -4051,35 +4055,23 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Knowsley</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>recycling</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>glencore britishvolt</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H90" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I90" s="2" t="n">
-        <v>44593</v>
-      </c>
+          <t>ford</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
     </row>
@@ -4089,12 +4081,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Knowsley</t>
+          <t>Komárom-Esztergom</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4102,17 +4094,33 @@
           <t>vehicle</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ford</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+          <t>byd</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>400</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>42644</v>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>42552</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>42826</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -4130,36 +4138,32 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>byd</t>
+          <t>huayou cobalt</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>400</v>
+        <v>100000</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>42644</v>
-      </c>
-      <c r="J92" s="2" t="n">
-        <v>42552</v>
-      </c>
-      <c r="K92" s="2" t="n">
-        <v>42826</v>
-      </c>
+        <v>45078</v>
+      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -4182,27 +4186,31 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>huayou cobalt</t>
+          <t>sk innovation</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>100</v>
+        <v>7.5</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>45078</v>
-      </c>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+        <v>43040</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>43160</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>44197</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -4210,46 +4218,42 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Komárom-Esztergom</t>
+          <t>Košice Region</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>sk innovation</t>
+          <t>volvo cars</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>7.5</v>
+        <v>250000</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>43040</v>
-      </c>
-      <c r="J94" s="2" t="n">
-        <v>43160</v>
-      </c>
-      <c r="K94" s="2" t="n">
-        <v>44197</v>
-      </c>
+        <v>44743</v>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -4277,7 +4281,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>volvo cars</t>
+          <t>zhi dou</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -4286,10 +4290,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>250000</v>
+        <v>60000</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>44743</v>
+        <v>43191</v>
       </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
@@ -4300,41 +4304,41 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Košice Region</t>
+          <t>Kymenlaakso</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>zhi dou</t>
+          <t>easpring finland new materials oy</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H96" t="n">
         <v>60000</v>
       </c>
-      <c r="I96" s="2" t="n">
-        <v>43191</v>
-      </c>
-      <c r="J96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" s="2" t="n">
+        <v>45717</v>
+      </c>
       <c r="K96" t="inlineStr"/>
     </row>
     <row r="97">
@@ -4363,21 +4367,21 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>easpring finland new materials oy</t>
+          <t>finnish minerals beijing easpring</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>60</v>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" s="2" t="n">
-        <v>45717</v>
-      </c>
+        <v>37.5</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>45139</v>
+      </c>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
@@ -4401,12 +4405,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>finnish minerals beijing easpring</t>
+          <t>finnish minerals group</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4415,7 +4419,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>37.5</v>
+        <v>33.5</v>
       </c>
       <c r="I98" s="2" t="n">
         <v>45139</v>
@@ -4429,42 +4433,42 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Kymenlaakso</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>deployment</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>finnish minerals group</t>
+          <t>baywa re</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="I99" s="2" t="n">
-        <v>45139</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" s="2" t="n">
+        <v>45566</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -4472,42 +4476,30 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>solar</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>deployment</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>baywa re</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H100" t="n">
-        <v>9</v>
-      </c>
+          <t>lotus</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
-      <c r="K100" s="2" t="n">
-        <v>45566</v>
-      </c>
+      <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -4515,12 +4507,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4528,10 +4520,14 @@
           <t>vehicle</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>lotus</t>
+          <t>electricbrands</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -4556,22 +4552,30 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>electricbrands</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
+          <t>gotion high tech</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>44409</v>
+      </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
     </row>
@@ -4596,7 +4600,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4639,26 +4643,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>gotion high tech</t>
+          <t>graphenix development inc</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H104" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I104" s="2" t="n">
-        <v>44409</v>
-      </c>
-      <c r="J104" t="inlineStr"/>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" s="2" t="n">
+        <v>45292</v>
+      </c>
       <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
@@ -4682,25 +4684,31 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>graphenix development inc</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>20</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>44317</v>
+      </c>
       <c r="J105" s="2" t="n">
-        <v>45292</v>
-      </c>
-      <c r="K105" t="inlineStr"/>
+        <v>45627</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>43586</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -4723,7 +4731,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4765,12 +4773,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4780,21 +4788,17 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>20</v>
+        <v>300000</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>44317</v>
-      </c>
-      <c r="J107" s="2" t="n">
-        <v>45627</v>
-      </c>
-      <c r="K107" s="2" t="n">
-        <v>43586</v>
-      </c>
+        <v>43709</v>
+      </c>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -4812,32 +4816,32 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>volkswagen group components</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>300000</v>
-      </c>
-      <c r="I108" s="2" t="n">
-        <v>43709</v>
-      </c>
+        <v>3600</v>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" s="2" t="n">
+        <v>44197</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -4860,27 +4864,27 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>recycling</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>volkswagen group components</t>
+          <t>volkswagen northvolt</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>3600</v>
+        <v>16</v>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" s="2" t="n">
-        <v>44197</v>
-      </c>
+      <c r="J109" s="2" t="n">
+        <v>43709</v>
+      </c>
+      <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -4888,12 +4892,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Lower Silesia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4901,28 +4905,24 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>volkswagen northvolt</t>
+          <t>lg chem</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>16</v>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" s="2" t="n">
-        <v>43709</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>42644</v>
+      </c>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
@@ -4944,25 +4944,29 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>module_pack</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>lg chem</t>
+          <t>lg energy solution</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>5</v>
-      </c>
-      <c r="I111" s="2" t="n">
-        <v>42644</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" s="2" t="n">
+        <v>45261</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -4970,12 +4974,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Lower Silesia</t>
+          <t>Molise</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4985,27 +4989,27 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>lg energy solution</t>
+          <t>automotive cell company</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>70</v>
-      </c>
-      <c r="I112" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>45444</v>
+      </c>
       <c r="J112" t="inlineStr"/>
-      <c r="K112" s="2" t="n">
-        <v>45261</v>
-      </c>
+      <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -5013,12 +5017,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Molise</t>
+          <t>Nitra Region</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5033,7 +5037,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
+          <t>gotion inobat batteries</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -5042,10 +5046,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>45444</v>
+        <v>45231</v>
       </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
@@ -5056,12 +5060,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Nitra Region</t>
+          <t>Nordland</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5076,21 +5080,21 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>gotion inobat batteries</t>
+          <t>freyr</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H114" t="n">
-        <v>20</v>
-      </c>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
       <c r="I114" s="2" t="n">
-        <v>45231</v>
-      </c>
-      <c r="J114" t="inlineStr"/>
+        <v>43678</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>44470</v>
+      </c>
       <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
@@ -5114,7 +5118,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5142,41 +5146,37 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Nordland</t>
+          <t>Normandy</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>eam</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>freyr</t>
+          <t>hopium</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>20000</v>
+      </c>
       <c r="I116" s="2" t="n">
-        <v>43678</v>
-      </c>
-      <c r="J116" s="2" t="n">
-        <v>44470</v>
-      </c>
+        <v>44805</v>
+      </c>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
@@ -5198,23 +5198,19 @@
           <t>vehicle</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>hopium</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H117" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I117" s="2" t="n">
-        <v>44805</v>
-      </c>
+          <t>renault</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
     </row>
@@ -5224,34 +5220,42 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Normandy</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>renault</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
+          <t>cylib</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>9125</v>
+      </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" s="2" t="n">
+        <v>45261</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -5269,32 +5273,24 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>recycling</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>cylib</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H119" t="n">
-        <v>9125</v>
-      </c>
+          <t>ego mobile</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
-      <c r="K119" s="2" t="n">
-        <v>45261</v>
-      </c>
+      <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -5322,7 +5318,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>ego mobile</t>
+          <t>ford</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
@@ -5347,23 +5343,29 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>ford</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr"/>
+          <t>fraunhofer ffb</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
+      <c r="J121" s="2" t="n">
+        <v>45444</v>
+      </c>
       <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
@@ -5382,29 +5384,31 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>fraunhofer ffb</t>
+          <t>nextego mobile</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" s="2" t="n">
-        <v>45444</v>
-      </c>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>45200</v>
+      </c>
+      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
@@ -5423,17 +5427,13 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>electric</t>
-        </is>
-      </c>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>nextego mobile</t>
+          <t>primobius</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -5442,10 +5442,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>45200</v>
+        <v>44317</v>
       </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
@@ -5469,25 +5469,29 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>eam</t>
+        </is>
+      </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>primobius</t>
+          <t>pure battery technologies</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I124" s="2" t="n">
-        <v>44317</v>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" s="2" t="n">
+        <v>44713</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -5508,29 +5512,23 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>eam</t>
-        </is>
-      </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>pure battery technologies</t>
+          <t>rwth aachen university</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H125" t="n">
-        <v>10</v>
-      </c>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" s="2" t="n">
-        <v>44713</v>
-      </c>
+      <c r="J125" s="2" t="n">
+        <v>45292</v>
+      </c>
+      <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -5538,12 +5536,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Northumberland</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5551,10 +5549,14 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>rwth aachen university</t>
+          <t>britishvolt</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -5562,10 +5564,14 @@
           <t>under construction</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
+      <c r="H126" t="n">
+        <v>4</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>44197</v>
+      </c>
       <c r="J126" s="2" t="n">
-        <v>45292</v>
+        <v>44531</v>
       </c>
       <c r="K126" t="inlineStr"/>
     </row>
@@ -5590,7 +5596,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5620,12 +5626,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Northumberland</t>
+          <t>Nouvelle-Aquitaine</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -5640,24 +5646,22 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>britishvolt</t>
+          <t>forsee power</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>4</v>
-      </c>
-      <c r="I128" s="2" t="n">
-        <v>44197</v>
-      </c>
-      <c r="J128" s="2" t="n">
-        <v>44531</v>
-      </c>
-      <c r="K128" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" s="2" t="n">
+        <v>44986</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -5685,22 +5689,14 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>forsee power</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H129" t="n">
-        <v>1</v>
-      </c>
+          <t>startec energy</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
-      <c r="K129" s="2" t="n">
-        <v>44986</v>
-      </c>
+      <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -5708,32 +5704,40 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Nouvelle-Aquitaine</t>
+          <t>Novo Mesto</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>startec energy</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
+          <t>revoz</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>150000</v>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>45474</v>
+      </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
     </row>
@@ -5743,27 +5747,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Novo Mesto</t>
+          <t>Opole Voivodeship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>deployment</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>revoz</t>
+          <t>ox2</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5772,10 +5776,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>150000</v>
+        <v>0.09</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>45474</v>
+        <v>45839</v>
       </c>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
@@ -5796,32 +5800,32 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>deployment</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>ox2</t>
+          <t>umicore</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>90</v>
-      </c>
-      <c r="I132" s="2" t="n">
-        <v>45839</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" s="2" t="n">
+        <v>44958</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -5829,12 +5833,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Opole Voivodeship</t>
+          <t>Ostrobothnia</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -5849,22 +5853,22 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>umicore</t>
+          <t>finnish minerals group epsilon advanced materials</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>20</v>
-      </c>
-      <c r="I133" t="inlineStr"/>
+        <v>50000</v>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>44866</v>
+      </c>
       <c r="J133" t="inlineStr"/>
-      <c r="K133" s="2" t="n">
-        <v>44958</v>
-      </c>
+      <c r="K133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -5892,7 +5896,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>finnish minerals group epsilon advanced materials</t>
+          <t>freyr battery</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5901,10 +5905,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>50</v>
+        <v>30000</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>44866</v>
+        <v>45566</v>
       </c>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
@@ -5935,7 +5939,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>freyr battery</t>
+          <t>johnson matthey</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5944,10 +5948,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>30</v>
+        <v>30000</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>45566</v>
+        <v>44287</v>
       </c>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
@@ -5958,40 +5962,32 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ostrobothnia</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>johnson matthey</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H136" t="n">
-        <v>30</v>
-      </c>
-      <c r="I136" s="2" t="n">
-        <v>44287</v>
-      </c>
+          <t>bmw</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
     </row>
@@ -6011,22 +6007,30 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>deployment</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>bmw</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
+          <t>photovolt development partners</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>45778</v>
+      </c>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
     </row>
@@ -6036,40 +6040,32 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Pest County</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>deployment</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>photovolt development partners</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H138" t="n">
-        <v>840</v>
-      </c>
-      <c r="I138" s="2" t="n">
-        <v>45778</v>
-      </c>
+          <t>samsung sdi</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
     </row>
@@ -6079,34 +6075,42 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Pest County</t>
+          <t>Piedmont</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>samsung sdi</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
+          <t>fiat chrysler</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>80000</v>
+      </c>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" s="2" t="n">
+        <v>43862</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -6124,32 +6128,32 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>fiat chrysler</t>
+          <t>italvolt</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>80000</v>
-      </c>
-      <c r="I140" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>44348</v>
+      </c>
       <c r="J140" t="inlineStr"/>
-      <c r="K140" s="2" t="n">
-        <v>43862</v>
-      </c>
+      <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -6167,32 +6171,32 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>italvolt</t>
+          <t>micro mobility</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>45</v>
-      </c>
-      <c r="I141" s="2" t="n">
-        <v>44348</v>
-      </c>
+        <v>7500</v>
+      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" s="2" t="n">
+        <v>44440</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -6213,29 +6217,17 @@
           <t>vehicle</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>electric</t>
-        </is>
-      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>micro mobility</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H142" t="n">
-        <v>7500</v>
-      </c>
+          <t>stellantis</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
-      <c r="K142" s="2" t="n">
-        <v>44440</v>
-      </c>
+      <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -6243,28 +6235,40 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>Pirkanmaa</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>recycling</t>
+        </is>
+      </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>stellantis</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
+          <t>fortum</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>44197</v>
+      </c>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
     </row>
@@ -6294,20 +6298,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>fortum</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H144" t="n">
-        <v>3000</v>
-      </c>
-      <c r="I144" s="2" t="n">
-        <v>44197</v>
-      </c>
+          <t>fortum battery recycling</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
     </row>
@@ -6317,12 +6313,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Pirkanmaa</t>
+          <t>Pomerania</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -6332,17 +6328,25 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>recycling</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>fortum battery recycling</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
+          <t>northvolt south bay solutions</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>43374</v>
+      </c>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
     </row>
@@ -6352,12 +6356,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Pomerania</t>
+          <t>Rheinland-Pfalz</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -6367,26 +6371,28 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>northvolt south bay solutions</t>
+          <t>automotive cell company</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>43374</v>
-      </c>
-      <c r="J146" t="inlineStr"/>
+        <v>43862</v>
+      </c>
+      <c r="J146" s="2" t="n">
+        <v>44440</v>
+      </c>
       <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
@@ -6410,7 +6416,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -6453,31 +6459,25 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>module_pack</t>
-        </is>
-      </c>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
+          <t>e lyte</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>8</v>
-      </c>
-      <c r="I148" s="2" t="n">
-        <v>43862</v>
-      </c>
-      <c r="J148" s="2" t="n">
-        <v>44440</v>
-      </c>
-      <c r="K148" t="inlineStr"/>
+        <v>20000</v>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" s="2" t="n">
+        <v>45536</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -6485,38 +6485,42 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Rheinland-Pfalz</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr"/>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>e lyte</t>
+          <t>sng solar</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I149" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>45839</v>
+      </c>
       <c r="J149" t="inlineStr"/>
-      <c r="K149" s="2" t="n">
-        <v>45536</v>
-      </c>
+      <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -6524,41 +6528,37 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Ruse</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>solar</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>deployment</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>sng solar</t>
+          <t>eberspacher</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H150" t="n">
-        <v>100</v>
-      </c>
-      <c r="I150" s="2" t="n">
-        <v>45839</v>
-      </c>
-      <c r="J150" t="inlineStr"/>
+        <v>2400000</v>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" s="2" t="n">
+        <v>45017</v>
+      </c>
       <c r="K150" t="inlineStr"/>
     </row>
     <row r="151">
@@ -6567,23 +6567,27 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Ruse</t>
+          <t>Saarland</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>eberspacher</t>
+          <t>svolt</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -6592,11 +6596,13 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="I151" t="inlineStr"/>
+        <v>297</v>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>44136</v>
+      </c>
       <c r="J151" s="2" t="n">
-        <v>45017</v>
+        <v>44531</v>
       </c>
       <c r="K151" t="inlineStr"/>
     </row>
@@ -6606,12 +6612,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Saarland</t>
+          <t>Sardinia</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -6621,28 +6627,26 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>svolt</t>
+          <t>li cycle glencore</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H152" t="n">
-        <v>297</v>
+        <v>60000</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>44136</v>
-      </c>
-      <c r="J152" s="2" t="n">
-        <v>44531</v>
-      </c>
+        <v>45139</v>
+      </c>
+      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
     </row>
     <row r="153">
@@ -6651,12 +6655,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Sardinia</t>
+          <t>Satakunta</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -6666,26 +6670,28 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>recycling</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>li cycle glencore</t>
+          <t>basf</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H153" t="n">
-        <v>60000</v>
+        <v>20</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>45139</v>
-      </c>
-      <c r="J153" t="inlineStr"/>
+        <v>43405</v>
+      </c>
+      <c r="J153" s="2" t="n">
+        <v>43983</v>
+      </c>
       <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
@@ -6694,12 +6700,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Satakunta</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -6709,29 +6715,31 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>basf</t>
+          <t>blackstone technology</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H154" t="n">
-        <v>20</v>
+        <v>0.5</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>43405</v>
+        <v>44228</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>43983</v>
-      </c>
-      <c r="K154" t="inlineStr"/>
+        <v>44440</v>
+      </c>
+      <c r="K154" s="2" t="n">
+        <v>43466</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -6754,31 +6762,19 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>blackstone technology</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H155" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I155" s="2" t="n">
-        <v>44228</v>
-      </c>
-      <c r="J155" s="2" t="n">
-        <v>44440</v>
-      </c>
-      <c r="K155" s="2" t="n">
-        <v>43466</v>
-      </c>
+          <t>bmw</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -6796,12 +6792,12 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -6831,22 +6827,30 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>ingot_wafer</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>bmw</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
+          <t>european semiconductor manufacturing company</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>480000</v>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>45627</v>
+      </c>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
     </row>
@@ -6866,30 +6870,22 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>ingot_wafer</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>european semiconductor manufacturing company</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H158" t="n">
-        <v>480000</v>
-      </c>
-      <c r="I158" s="2" t="n">
-        <v>45627</v>
-      </c>
+          <t>jt energy systems</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
     </row>
@@ -6909,17 +6905,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>jt energy systems</t>
+          <t>meyer burger</t>
         </is>
       </c>
       <c r="G159" t="inlineStr"/>
@@ -6944,22 +6940,30 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>meyer burger</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
+          <t>volkswagen</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
+        <v>109500</v>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>42856</v>
+      </c>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
     </row>
@@ -6974,7 +6978,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -6982,24 +6986,28 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>eam</t>
+        </is>
+      </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>porsche</t>
+          <t>amg lithium</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H161" t="n">
-        <v>24</v>
-      </c>
-      <c r="I161" s="2" t="n">
-        <v>45566</v>
-      </c>
-      <c r="J161" t="inlineStr"/>
+        <v>20000</v>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" s="2" t="n">
+        <v>45047</v>
+      </c>
       <c r="K161" t="inlineStr"/>
     </row>
     <row r="162">
@@ -7013,37 +7021,33 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>electric</t>
-        </is>
-      </c>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>battery lifecycle company</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H162" t="n">
-        <v>109500</v>
-      </c>
-      <c r="I162" s="2" t="n">
-        <v>42856</v>
-      </c>
+        <v>15000</v>
+      </c>
+      <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" s="2" t="n">
+        <v>45505</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -7066,26 +7070,26 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>amg lithium</t>
+          <t>farasis energy</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H163" t="n">
-        <v>20</v>
-      </c>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" s="2" t="n">
-        <v>45047</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>44228</v>
+      </c>
+      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
     </row>
     <row r="164">
@@ -7107,25 +7111,21 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>battery lifecycle company</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H164" t="n">
-        <v>15000</v>
-      </c>
+          <t>farasis energy europe</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr"/>
-      <c r="K164" s="2" t="n">
-        <v>45505</v>
-      </c>
+      <c r="K164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -7148,27 +7148,29 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>farasis energy</t>
+          <t>li cycle</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H165" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I165" s="2" t="n">
-        <v>44228</v>
-      </c>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
+        <v>10000</v>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" s="2" t="n">
+        <v>44986</v>
+      </c>
+      <c r="K165" s="2" t="n">
+        <v>45139</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -7191,18 +7193,24 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>farasis energy europe</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr"/>
+          <t>norcsi</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
+      <c r="J166" s="2" t="n">
+        <v>45839</v>
+      </c>
       <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
@@ -7216,7 +7224,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Schleswig-Holstein</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -7226,29 +7234,29 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>recycling</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>li cycle</t>
+          <t>northvolt</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H167" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I167" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="I167" s="2" t="n">
+        <v>44621</v>
+      </c>
       <c r="J167" s="2" t="n">
-        <v>44986</v>
-      </c>
-      <c r="K167" s="2" t="n">
-        <v>45139</v>
-      </c>
+        <v>45352</v>
+      </c>
+      <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -7256,12 +7264,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Schwyz</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -7269,14 +7277,10 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>eam</t>
-        </is>
-      </c>
+      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>norcsi</t>
+          <t>ecovolta</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -7284,10 +7288,12 @@
           <t>under construction</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr"/>
+      <c r="H168" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I168" t="inlineStr"/>
       <c r="J168" s="2" t="n">
-        <v>45839</v>
+        <v>43252</v>
       </c>
       <c r="K168" t="inlineStr"/>
     </row>
@@ -7297,12 +7303,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Schleswig-Holstein</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -7317,23 +7323,21 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>northvolt</t>
+          <t>calb</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H169" t="n">
         <v>15</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>44621</v>
-      </c>
-      <c r="J169" s="2" t="n">
-        <v>45352</v>
-      </c>
+        <v>44866</v>
+      </c>
+      <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
     </row>
     <row r="170">
@@ -7342,12 +7346,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Schwyz</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -7355,24 +7359,28 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>module_pack</t>
+        </is>
+      </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>ecovolta</t>
+          <t>calb</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H170" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" s="2" t="n">
-        <v>43252</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>44866</v>
+      </c>
+      <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
     </row>
     <row r="171">
@@ -7391,17 +7399,13 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>calb</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -7410,10 +7414,10 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>15</v>
+        <v>100000</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>44866</v>
+        <v>45748</v>
       </c>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
@@ -7424,12 +7428,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Silesia</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -7439,27 +7443,29 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>calb</t>
+          <t>ae elemental</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H172" t="n">
-        <v>15</v>
+        <v>12000</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>44866</v>
+        <v>45383</v>
       </c>
       <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" s="2" t="n">
+        <v>45536</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -7467,12 +7473,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Silesia</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -7483,7 +7489,7 @@
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -7492,10 +7498,10 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>45748</v>
+        <v>44958</v>
       </c>
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr"/>
@@ -7506,12 +7512,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Silesia</t>
+          <t>Solothurn</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -7526,7 +7532,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>ae elemental</t>
+          <t>librec</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -7537,12 +7543,10 @@
       <c r="H174" t="n">
         <v>12000</v>
       </c>
-      <c r="I174" s="2" t="n">
-        <v>45383</v>
-      </c>
+      <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr"/>
       <c r="K174" s="2" t="n">
-        <v>45536</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="175">
@@ -7551,37 +7555,43 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Silesia</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>agratas</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H175" t="n">
-        <v>10000</v>
+        <v>40</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>44958</v>
-      </c>
-      <c r="J175" t="inlineStr"/>
+        <v>45108</v>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>45689</v>
+      </c>
       <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
@@ -7590,12 +7600,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Solothurn</t>
+          <t>Southwest Finland</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -7605,27 +7615,19 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>recycling</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>librec</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H176" t="n">
-        <v>12000</v>
-      </c>
+          <t>valmet automotive</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
-      <c r="K176" s="2" t="n">
-        <v>45778</v>
-      </c>
+      <c r="K176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
@@ -7633,43 +7635,37 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Southwest Finland</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>agratas</t>
+          <t>valmet automotive</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H177" t="n">
-        <v>40</v>
+        <v>257000</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>45108</v>
-      </c>
-      <c r="J177" s="2" t="n">
-        <v>45689</v>
-      </c>
+        <v>44652</v>
+      </c>
+      <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
     </row>
     <row r="178">
@@ -7678,27 +7674,27 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Southwest Finland</t>
+          <t>State of Berlin</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>valmet automotive</t>
+          <t>tesla</t>
         </is>
       </c>
       <c r="G178" t="inlineStr"/>
@@ -7713,38 +7709,46 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Southwest Finland</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>valmet automotive</t>
+          <t>aesc</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H179" t="n">
-        <v>257000</v>
+        <v>1.8</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>44652</v>
-      </c>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
+        <v>44317</v>
+      </c>
+      <c r="J179" s="2" t="n">
+        <v>44470</v>
+      </c>
+      <c r="K179" s="2" t="n">
+        <v>45292</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
@@ -7752,34 +7756,46 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>State of Berlin</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>tesla</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
+          <t>aesc</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H180" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>44317</v>
+      </c>
+      <c r="J180" s="2" t="n">
+        <v>44470</v>
+      </c>
+      <c r="K180" s="2" t="n">
+        <v>45292</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
@@ -7807,26 +7823,24 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>aesc</t>
+          <t>nissan</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H181" t="n">
-        <v>1.8</v>
+        <v>35</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>44317</v>
+        <v>44896</v>
       </c>
       <c r="J181" s="2" t="n">
-        <v>44470</v>
-      </c>
-      <c r="K181" s="2" t="n">
-        <v>45292</v>
-      </c>
+        <v>45231</v>
+      </c>
+      <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
@@ -7844,36 +7858,32 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>aesc</t>
+          <t>nissan</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H182" t="n">
-        <v>1.8</v>
-      </c>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
       <c r="I182" s="2" t="n">
-        <v>44317</v>
+        <v>44378</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>44470</v>
-      </c>
-      <c r="K182" s="2" t="n">
-        <v>45292</v>
-      </c>
+        <v>45352</v>
+      </c>
+      <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
@@ -7891,33 +7901,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>nissan</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H183" t="n">
-        <v>35</v>
-      </c>
-      <c r="I183" s="2" t="n">
-        <v>44896</v>
-      </c>
-      <c r="J183" s="2" t="n">
-        <v>45231</v>
-      </c>
+          <t>saietta group</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
@@ -7926,42 +7922,42 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Telemark</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>nissan</t>
+          <t>vianode</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" s="2" t="n">
-        <v>44378</v>
-      </c>
-      <c r="J184" s="2" t="n">
-        <v>45352</v>
-      </c>
-      <c r="K184" t="inlineStr"/>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H184" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" s="2" t="n">
+        <v>45566</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
@@ -7969,30 +7965,44 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Thuringia</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>saietta group</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr"/>
-      <c r="H185" t="inlineStr"/>
-      <c r="I185" t="inlineStr"/>
+          <t>catl</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H185" t="n">
+        <v>8</v>
+      </c>
+      <c r="I185" s="2" t="n">
+        <v>43282</v>
+      </c>
       <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" s="2" t="n">
+        <v>44501</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
@@ -8000,12 +8010,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Telemark</t>
+          <t>Thuringia</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -8015,27 +8025,27 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>vianode</t>
+          <t>lion smart</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H186" t="n">
-        <v>2</v>
+        <v>240</v>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" s="2" t="n">
-        <v>45566</v>
-      </c>
+      <c r="J186" s="2" t="n">
+        <v>45139</v>
+      </c>
+      <c r="K186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
@@ -8058,29 +8068,27 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>catl</t>
+          <t>sungeel hitech and samsung</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H187" t="n">
-        <v>8</v>
+        <v>20000</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>43282</v>
+        <v>45170</v>
       </c>
       <c r="J187" t="inlineStr"/>
-      <c r="K187" s="2" t="n">
-        <v>44501</v>
-      </c>
+      <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
@@ -8088,12 +8096,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Thuringia</t>
+          <t>Trnava Region</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -8103,26 +8111,26 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>lion smart</t>
+          <t>gotion inobat batteries</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H188" t="n">
-        <v>240</v>
-      </c>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" s="2" t="n">
-        <v>45139</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I188" s="2" t="n">
+        <v>45261</v>
+      </c>
+      <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
@@ -8131,12 +8139,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Thuringia</t>
+          <t>Trnava Region</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -8146,27 +8154,31 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>recycling</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>sungeel hitech and samsung</t>
+          <t>inobat</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H189" t="n">
-        <v>20000</v>
+        <v>2.5</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>45170</v>
-      </c>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
+        <v>44105</v>
+      </c>
+      <c r="J189" s="2" t="n">
+        <v>44317</v>
+      </c>
+      <c r="K189" s="2" t="n">
+        <v>45261</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
@@ -8189,27 +8201,31 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>gotion inobat batteries</t>
+          <t>inobat</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H190" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="I190" s="2" t="n">
+        <v>44105</v>
+      </c>
+      <c r="J190" s="2" t="n">
+        <v>44317</v>
+      </c>
+      <c r="K190" s="2" t="n">
         <v>45261</v>
       </c>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
@@ -8217,12 +8233,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Trnava Region</t>
+          <t>Trøndelag</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -8237,26 +8253,20 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>inobat</t>
+          <t>elinor batteries</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H191" t="n">
-        <v>2.5</v>
-      </c>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr"/>
       <c r="I191" s="2" t="n">
-        <v>44105</v>
-      </c>
-      <c r="J191" s="2" t="n">
-        <v>44317</v>
-      </c>
-      <c r="K191" s="2" t="n">
-        <v>45261</v>
-      </c>
+        <v>44927</v>
+      </c>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
@@ -8264,46 +8274,42 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Trnava Region</t>
+          <t>Tukums Municipality</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>deployment</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>inobat</t>
+          <t>ignitis renewables</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H192" t="n">
-        <v>2.5</v>
+        <v>0.174</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>44105</v>
-      </c>
-      <c r="J192" s="2" t="n">
-        <v>44317</v>
-      </c>
-      <c r="K192" s="2" t="n">
-        <v>45261</v>
-      </c>
+        <v>45839</v>
+      </c>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
@@ -8311,39 +8317,37 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Trøndelag</t>
+          <t>Utena</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
-          <t>elinor batteries</t>
+          <t>european energy</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" s="2" t="n">
-        <v>44927</v>
-      </c>
-      <c r="J193" t="inlineStr"/>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H193" t="n">
+        <v>0.0785</v>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" s="2" t="n">
+        <v>45809</v>
+      </c>
       <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
@@ -8352,41 +8356,43 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Tukums Municipality</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>deployment</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>ignitis renewables</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H194" t="n">
-        <v>174</v>
+        <v>40</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>45839</v>
-      </c>
-      <c r="J194" t="inlineStr"/>
+        <v>44593</v>
+      </c>
+      <c r="J194" s="2" t="n">
+        <v>45566</v>
+      </c>
       <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
@@ -8395,23 +8401,27 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Utena</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>solar</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>eam</t>
+        </is>
+      </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>european energy</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -8420,11 +8430,13 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="I195" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="I195" s="2" t="n">
+        <v>44593</v>
+      </c>
       <c r="J195" s="2" t="n">
-        <v>45809</v>
+        <v>45566</v>
       </c>
       <c r="K195" t="inlineStr"/>
     </row>
@@ -8444,12 +8456,12 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -8459,18 +8471,16 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H196" t="n">
         <v>40</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>44593</v>
-      </c>
-      <c r="J196" s="2" t="n">
-        <v>45566</v>
-      </c>
+        <v>44927</v>
+      </c>
+      <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr"/>
     </row>
     <row r="197">
@@ -8479,27 +8489,23 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Vas County</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>eam</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>schaeffler</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -8508,13 +8514,11 @@
         </is>
       </c>
       <c r="H197" t="n">
-        <v>40</v>
-      </c>
-      <c r="I197" s="2" t="n">
-        <v>44593</v>
-      </c>
+        <v>800000</v>
+      </c>
+      <c r="I197" t="inlineStr"/>
       <c r="J197" s="2" t="n">
-        <v>45566</v>
+        <v>44440</v>
       </c>
       <c r="K197" t="inlineStr"/>
     </row>
@@ -8524,12 +8528,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Viseu</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -8544,20 +8548,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>volkswagen</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H198" t="n">
-        <v>40</v>
-      </c>
-      <c r="I198" s="2" t="n">
-        <v>44927</v>
-      </c>
+          <t>stellantis</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr"/>
     </row>
@@ -8567,12 +8563,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Vas County</t>
+          <t>Warwickshire</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -8580,25 +8576,29 @@
           <t>vehicle</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>schaeffler</t>
+          <t>london taxi company</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H199" t="n">
-        <v>800000</v>
+        <v>20000</v>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="J199" s="2" t="n">
-        <v>44440</v>
-      </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" s="2" t="n">
+        <v>42795</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
@@ -8606,34 +8606,42 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Viseu</t>
+          <t>Wolverhampton</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>stellantis</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr"/>
+          <t>recyclus group</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H200" t="n">
+        <v>22000</v>
+      </c>
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" s="2" t="n">
+        <v>45200</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
@@ -8641,27 +8649,23 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Warwickshire</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>electric</t>
-        </is>
-      </c>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>london taxi company</t>
+          <t>battrion</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -8670,12 +8674,12 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>20000</v>
+        <v>0.02</v>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr"/>
       <c r="K201" s="2" t="n">
-        <v>42795</v>
+        <v>44287</v>
       </c>
     </row>
     <row r="202">
@@ -8684,12 +8688,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Wolverhampton</t>
+          <t>Île-de-France</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -8704,22 +8708,22 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>recyclus group</t>
+          <t>lg energy solution derichebourg</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H202" t="n">
-        <v>22000</v>
-      </c>
-      <c r="I202" t="inlineStr"/>
+        <v>20000</v>
+      </c>
+      <c r="I202" s="2" t="n">
+        <v>45748</v>
+      </c>
       <c r="J202" t="inlineStr"/>
-      <c r="K202" s="2" t="n">
-        <v>45200</v>
-      </c>
+      <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
@@ -8727,12 +8731,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Østfold</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -8740,10 +8744,14 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>recycling</t>
+        </is>
+      </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>battrion</t>
+          <t>hydrovolt</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -8752,12 +8760,14 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>0.02</v>
+        <v>12000</v>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
+      <c r="J203" s="2" t="n">
+        <v>44228</v>
+      </c>
       <c r="K203" s="2" t="n">
-        <v>44287</v>
+        <v>44228</v>
       </c>
     </row>
     <row r="204">
@@ -8766,12 +8776,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Île-de-France</t>
+          <t>Świętokrzyskie</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -8781,113 +8791,25 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>recycling</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>lg energy solution derichebourg</t>
+          <t>green cell</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H204" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I204" s="2" t="n">
-        <v>45748</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
-    </row>
-    <row r="205">
-      <c r="A205" s="1" t="n">
-        <v>203</v>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Østfold</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>recycling</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>hydrovolt</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H205" t="n">
-        <v>12000</v>
-      </c>
-      <c r="I205" t="inlineStr"/>
-      <c r="J205" s="2" t="n">
-        <v>44228</v>
-      </c>
-      <c r="K205" s="2" t="n">
-        <v>44228</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="1" t="n">
-        <v>204</v>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Świętokrzyskie</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>module_pack</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>green cell</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H206" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
-      <c r="K206" s="2" t="n">
+      <c r="K204" s="2" t="n">
         <v>44652</v>
       </c>
     </row>

--- a/reconcile/storage/output/capacities_plot.xlsx
+++ b/reconcile/storage/output/capacities_plot.xlsx
@@ -1484,9 +1484,7 @@
           <t>operational</t>
         </is>
       </c>
-      <c r="H26" t="n">
-        <v>0.025</v>
-      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" s="2" t="n">
@@ -1558,9 +1556,7 @@
           <t>operational</t>
         </is>
       </c>
-      <c r="H28" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" s="2" t="n">
         <v>45597</v>
       </c>
@@ -2472,9 +2468,7 @@
           <t>operational</t>
         </is>
       </c>
-      <c r="H50" t="n">
-        <v>0.0025</v>
-      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" s="2" t="n">
@@ -3838,9 +3832,7 @@
           <t>announced</t>
         </is>
       </c>
-      <c r="H84" t="n">
-        <v>15</v>
-      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" s="2" t="n">
         <v>44713</v>
       </c>
@@ -5248,9 +5240,7 @@
           <t>operational</t>
         </is>
       </c>
-      <c r="H118" t="n">
-        <v>9125</v>
-      </c>
+      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" s="2" t="n">
@@ -6341,9 +6331,7 @@
           <t>announced</t>
         </is>
       </c>
-      <c r="H145" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="H145" t="inlineStr"/>
       <c r="I145" s="2" t="n">
         <v>43374</v>
       </c>
@@ -6845,9 +6833,7 @@
           <t>announced</t>
         </is>
       </c>
-      <c r="H157" t="n">
-        <v>480000</v>
-      </c>
+      <c r="H157" t="inlineStr"/>
       <c r="I157" s="2" t="n">
         <v>45627</v>
       </c>
@@ -7083,9 +7069,7 @@
           <t>announced</t>
         </is>
       </c>
-      <c r="H163" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="H163" t="inlineStr"/>
       <c r="I163" s="2" t="n">
         <v>44228</v>
       </c>
@@ -8038,9 +8022,7 @@
           <t>under construction</t>
         </is>
       </c>
-      <c r="H186" t="n">
-        <v>240</v>
-      </c>
+      <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
       <c r="J186" s="2" t="n">
         <v>45139</v>
@@ -8167,9 +8149,7 @@
           <t>operational</t>
         </is>
       </c>
-      <c r="H189" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="H189" t="inlineStr"/>
       <c r="I189" s="2" t="n">
         <v>44105</v>
       </c>
@@ -8214,9 +8194,7 @@
           <t>operational</t>
         </is>
       </c>
-      <c r="H190" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="H190" t="inlineStr"/>
       <c r="I190" s="2" t="n">
         <v>44105</v>
       </c>
@@ -8804,9 +8782,7 @@
           <t>operational</t>
         </is>
       </c>
-      <c r="H204" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr"/>
       <c r="K204" s="2" t="n">

--- a/reconcile/storage/output/capacities_plot.xlsx
+++ b/reconcile/storage/output/capacities_plot.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K204"/>
+  <dimension ref="A1:K211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -895,7 +895,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" s="2" t="n">
-        <v>45778</v>
+        <v>44986</v>
       </c>
     </row>
     <row r="12">
@@ -1790,36 +1790,28 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>eam</t>
-        </is>
-      </c>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>basf</t>
+          <t>ampyr solar europe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>15000</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>44713</v>
-      </c>
+        <v>0.045</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" s="2" t="n">
-        <v>43983</v>
-      </c>
-      <c r="K34" s="2" t="n">
-        <v>45078</v>
-      </c>
+        <v>45748</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -1842,7 +1834,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>recycling</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1889,12 +1881,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>microvast gmbh</t>
+          <t>basf</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1903,12 +1895,16 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+        <v>15000</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>44713</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>43983</v>
+      </c>
       <c r="K36" s="2" t="n">
-        <v>44228</v>
+        <v>45078</v>
       </c>
     </row>
     <row r="37">
@@ -1927,17 +1923,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>module</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>oxford pv</t>
+          <t>microvast gmbh</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1946,12 +1942,12 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" s="2" t="n">
-        <v>45536</v>
+        <v>44228</v>
       </c>
     </row>
     <row r="38">
@@ -1970,24 +1966,32 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>module</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>svolt</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+          <t>oxford pv</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1</v>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" s="2" t="n">
+        <v>45536</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -2015,20 +2019,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>tesla</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>50</v>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>44197</v>
-      </c>
+          <t>svolt</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
     </row>
@@ -2048,12 +2044,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2063,21 +2059,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>500000</v>
+        <v>50</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>43800</v>
-      </c>
-      <c r="J40" s="2" t="n">
-        <v>44256</v>
-      </c>
-      <c r="K40" s="2" t="n">
-        <v>44621</v>
-      </c>
+        <v>44197</v>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -2085,42 +2077,46 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bratislava Region</t>
+          <t>Brandenburg</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>inobat</t>
+          <t>tesla</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>10</v>
+        <v>500000</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>44105</v>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+        <v>43800</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>44256</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>44621</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -2138,13 +2134,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>inobat</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>200000</v>
+        <v>10</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>43709</v>
+        <v>44105</v>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
@@ -2167,12 +2167,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brussels Capital</t>
+          <t>Bratislava Region</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2180,19 +2180,23 @@
           <t>vehicle</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>electric</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>audi</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+          <t>volkswagen</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>43709</v>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
     </row>
@@ -2202,40 +2206,32 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Budapest</t>
+          <t>Brussels Capital</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>samsung sdi</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>42583</v>
-      </c>
+          <t>audi</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
     </row>
@@ -2245,38 +2241,42 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Catalonia</t>
+          <t>Budapest</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>module_pack</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>seat</t>
+          <t>samsung sdi</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>100000</v>
-      </c>
-      <c r="I45" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>42583</v>
+      </c>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" s="2" t="n">
-        <v>45748</v>
-      </c>
+      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -2284,32 +2284,36 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>City state Bremen</t>
+          <t>Castille-La Mancha</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>recycling</t>
-        </is>
-      </c>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>redux recycling</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+          <t>solaria</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45778</v>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
     </row>
@@ -2319,42 +2323,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Catalonia</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>eve energy</t>
+          <t>seat</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>20</v>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>45352</v>
-      </c>
+        <v>100000</v>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" s="2" t="n">
+        <v>45748</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -2362,38 +2362,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>City state Bremen</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>recycling</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>levc</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
-        <v>24000</v>
-      </c>
+          <t>redux recycling</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" s="2" t="n">
-        <v>42917</v>
-      </c>
+      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -2411,13 +2407,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>red sun group</t>
+          <t>eve energy</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>300000</v>
+        <v>20</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>43252</v>
+        <v>45352</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
@@ -2450,17 +2450,13 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>module_pack</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>uk battery industrialisation centre</t>
+          <t>levc</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2468,11 +2464,13 @@
           <t>operational</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
+      <c r="H50" t="n">
+        <v>24000</v>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" s="2" t="n">
-        <v>44228</v>
+        <v>42917</v>
       </c>
     </row>
     <row r="51">
@@ -2491,17 +2489,13 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>volklec</t>
+          <t>red sun group</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2510,10 +2504,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.1</v>
+        <v>300000</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45717</v>
+        <v>43252</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
@@ -2539,27 +2533,25 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>west midlands gigafactory</t>
+          <t>uk battery industrialisation centre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>60</v>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>44470</v>
-      </c>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" s="2" t="n">
+        <v>44228</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -2567,27 +2559,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Csongrád</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>build your dreams</t>
+          <t>volklec</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2596,10 +2588,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>200000</v>
+        <v>0.1</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45261</v>
+        <v>45717</v>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
@@ -2615,7 +2607,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dundee City</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2630,12 +2622,20 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>amte power</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
+          <t>west midlands gigafactory</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>60</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>44470</v>
+      </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
     </row>
@@ -2645,27 +2645,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Extremadura</t>
+          <t>Csongrád</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>aesc</t>
+          <t>build your dreams</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>50</v>
+        <v>200000</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>44652</v>
+        <v>45261</v>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
@@ -2688,42 +2688,34 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Extremadura</t>
+          <t>Dundee City</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>deployment</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>plenitude</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H56" t="n">
-        <v>0.13</v>
-      </c>
+          <t>amte power</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" s="2" t="n">
-        <v>45809</v>
-      </c>
+      <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -2731,12 +2723,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fejér</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2751,7 +2743,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>sk innovation</t>
+          <t>aesc</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2760,10 +2752,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>44197</v>
+        <v>44652</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
@@ -2774,34 +2766,42 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Flanders</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>recycling</t>
+          <t>deployment</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>umicore</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+          <t>plenitude</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>0.13</v>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" s="2" t="n">
+        <v>45809</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Flanders</t>
+          <t>Fejér</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2822,15 +2822,27 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>volvo cars</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
+          <t>sk innovation</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>10</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>44197</v>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
     </row>
@@ -2850,13 +2862,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>recycling</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>volvo cars</t>
+          <t>umicore</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -2871,12 +2887,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Galați County</t>
+          <t>Flanders</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2884,27 +2900,15 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>avesta battery and energy engineering</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H61" t="n">
-        <v>22</v>
-      </c>
-      <c r="I61" s="2" t="n">
-        <v>45078</v>
-      </c>
+          <t>volvo cars</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
     </row>
@@ -2914,12 +2918,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Grand Est</t>
+          <t>Flanders</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2930,7 +2934,7 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>psa</t>
+          <t>volvo cars</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -2945,32 +2949,40 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Greater London</t>
+          <t>Galați County</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>levc</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
+          <t>avesta battery and energy engineering</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>22</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45078</v>
+      </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
     </row>
@@ -2980,32 +2992,40 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Greater Poland</t>
+          <t>Grand Est</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>module</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>johnson matthey</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
+          <t>holosolis</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>5</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45474</v>
+      </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
     </row>
@@ -3015,12 +3035,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Győr-Moson-Sopron</t>
+          <t>Grand Est</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3031,7 +3051,7 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>audi</t>
+          <t>psa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -3046,12 +3066,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hajdú-Bihar</t>
+          <t>Greater London</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3061,28 +3081,18 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>bmw</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H66" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I66" s="2" t="n">
-        <v>43282</v>
-      </c>
-      <c r="J66" s="2" t="n">
-        <v>44713</v>
-      </c>
+          <t>levc</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
@@ -3091,12 +3101,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hajdú-Bihar</t>
+          <t>Greater Poland</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3106,28 +3116,18 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>catl</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H67" t="n">
-        <v>100</v>
-      </c>
-      <c r="I67" s="2" t="n">
-        <v>44774</v>
-      </c>
-      <c r="J67" s="2" t="n">
-        <v>45778</v>
-      </c>
+          <t>johnson matthey</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
@@ -3141,38 +3141,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hajdú-Bihar</t>
+          <t>Győr-Moson-Sopron</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>eam</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ecopro bm</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H68" t="n">
-        <v>108000</v>
-      </c>
-      <c r="I68" s="2" t="n">
-        <v>44531</v>
-      </c>
-      <c r="J68" s="2" t="n">
-        <v>45017</v>
-      </c>
+          <t>audi</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
@@ -3191,17 +3177,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>eve energy</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3210,13 +3196,13 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>28</v>
+        <v>150000</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>44774</v>
+        <v>43282</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>45200</v>
+        <v>44713</v>
       </c>
       <c r="K69" t="inlineStr"/>
     </row>
@@ -3226,12 +3212,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Hajdú-Bihar</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3241,27 +3227,29 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>recycling</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>emr</t>
+          <t>catl</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" s="2" t="n">
-        <v>45139</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>44774</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>45778</v>
+      </c>
+      <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -3269,12 +3257,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Hajdú-Bihar</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3284,18 +3272,28 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ilika</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+          <t>ecopro bm</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>108000</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>44531</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>45017</v>
+      </c>
       <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
@@ -3304,12 +3302,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hajdú-Bihar</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3324,7 +3322,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>aesc</t>
+          <t>eve energy</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3333,13 +3331,13 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>44348</v>
+        <v>44774</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>45231</v>
+        <v>45200</v>
       </c>
       <c r="K72" t="inlineStr"/>
     </row>
@@ -3349,12 +3347,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3364,29 +3362,27 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
+          <t>emr</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>13</v>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>44287</v>
-      </c>
-      <c r="J73" s="2" t="n">
-        <v>45047</v>
-      </c>
-      <c r="K73" t="inlineStr"/>
+        <v>10000</v>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" s="2" t="n">
+        <v>45139</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -3394,12 +3390,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3409,28 +3405,18 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H74" t="n">
-        <v>13</v>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>44287</v>
-      </c>
-      <c r="J74" s="2" t="n">
-        <v>45047</v>
-      </c>
+          <t>ilika</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
@@ -3459,22 +3445,24 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>automotive energy supply company</t>
+          <t>aesc</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>10</v>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" s="2" t="n">
-        <v>45809</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>44348</v>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>45231</v>
+      </c>
+      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -3497,27 +3485,29 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>automotive energy supply company</t>
+          <t>automotive cell company</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>10</v>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" s="2" t="n">
-        <v>45809</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>44287</v>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>45047</v>
+      </c>
+      <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -3535,31 +3525,33 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>byd</t>
+          <t>automotive cell company</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>200</v>
+        <v>13</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>42795</v>
-      </c>
-      <c r="J77" t="inlineStr"/>
+        <v>44287</v>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>45047</v>
+      </c>
       <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
@@ -3583,27 +3575,27 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>recycling</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>eramet suez</t>
+          <t>automotive energy supply company</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>50000</v>
-      </c>
-      <c r="I78" s="2" t="n">
-        <v>45231</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" s="2" t="n">
+        <v>45809</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -3626,27 +3618,27 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>li cycle</t>
+          <t>automotive energy supply company</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I79" s="2" t="n">
-        <v>44986</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" s="2" t="n">
+        <v>45809</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -3664,17 +3656,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>prologium</t>
+          <t>byd</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3682,9 +3674,11 @@
           <t>announced</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
+      <c r="H80" t="n">
+        <v>200</v>
+      </c>
       <c r="I80" s="2" t="n">
-        <v>45078</v>
+        <v>42795</v>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
@@ -3710,17 +3704,25 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>renault</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
+          <t>eramet suez</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>50000</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>45231</v>
+      </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
     </row>
@@ -3740,22 +3742,30 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>renault</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
+          <t>li cycle</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>44986</v>
+      </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
     </row>
@@ -3778,10 +3788,14 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>renault group</t>
+          <t>prologium</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3789,11 +3803,9 @@
           <t>announced</t>
         </is>
       </c>
-      <c r="H83" t="n">
-        <v>9</v>
-      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" s="2" t="n">
-        <v>44440</v>
+        <v>45078</v>
       </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
@@ -3819,23 +3831,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>renault minth</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
+          <t>renault</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
-      <c r="I84" s="2" t="n">
-        <v>44713</v>
-      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
     </row>
@@ -3855,17 +3861,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>saft</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -3890,18 +3896,26 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>toyota motor europe</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
+          <t>renault group</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>9</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>44440</v>
+      </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
     </row>
@@ -3926,28 +3940,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>verkor</t>
+          <t>renault minth</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H87" t="n">
-        <v>16</v>
-      </c>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" s="2" t="n">
-        <v>44593</v>
-      </c>
-      <c r="J87" s="2" t="n">
-        <v>45200</v>
-      </c>
+        <v>44713</v>
+      </c>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
@@ -3956,12 +3966,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hesse</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3971,27 +3981,19 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>akasol</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H88" t="n">
-        <v>1</v>
-      </c>
+          <t>saft</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" s="2" t="n">
-        <v>43191</v>
-      </c>
+      <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -3999,40 +4001,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>recycling</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>glencore britishvolt</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H89" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I89" s="2" t="n">
-        <v>44593</v>
-      </c>
+          <t>toyota motor europe</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
     </row>
@@ -4042,29 +4032,43 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Knowsley</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ford</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
+          <t>verkor</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>16</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>44593</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>45200</v>
+      </c>
       <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
@@ -4073,27 +4077,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Komárom-Esztergom</t>
+          <t>Hesse</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>byd</t>
+          <t>akasol</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4102,16 +4106,12 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>400</v>
-      </c>
-      <c r="I91" s="2" t="n">
-        <v>42644</v>
-      </c>
-      <c r="J91" s="2" t="n">
-        <v>42552</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" s="2" t="n">
-        <v>42826</v>
+        <v>43191</v>
       </c>
     </row>
     <row r="92">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Komárom-Esztergom</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>huayou cobalt</t>
+          <t>glencore britishvolt</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>45078</v>
+        <v>44593</v>
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
@@ -4163,46 +4163,30 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Komárom-Esztergom</t>
+          <t>Knowsley</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>sk innovation</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H93" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I93" s="2" t="n">
-        <v>43040</v>
-      </c>
-      <c r="J93" s="2" t="n">
-        <v>43160</v>
-      </c>
-      <c r="K93" s="2" t="n">
-        <v>44197</v>
-      </c>
+          <t>ford</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -4210,12 +4194,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Košice Region</t>
+          <t>Komárom-Esztergom</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4230,22 +4214,26 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>volvo cars</t>
+          <t>byd</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>250000</v>
+        <v>400</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>44743</v>
-      </c>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
+        <v>42644</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>42552</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>42826</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -4253,27 +4241,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Košice Region</t>
+          <t>Komárom-Esztergom</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>zhi dou</t>
+          <t>huayou cobalt</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -4282,10 +4270,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>60000</v>
+        <v>100000</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>43191</v>
+        <v>45078</v>
       </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
@@ -4296,12 +4284,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Kymenlaakso</t>
+          <t>Komárom-Esztergom</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4311,27 +4299,31 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>easpring finland new materials oy</t>
+          <t>sk innovation</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>60000</v>
-      </c>
-      <c r="I96" t="inlineStr"/>
+        <v>7.5</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>43040</v>
+      </c>
       <c r="J96" s="2" t="n">
-        <v>45717</v>
-      </c>
-      <c r="K96" t="inlineStr"/>
+        <v>43160</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>44197</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -4339,27 +4331,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Kymenlaakso</t>
+          <t>Košice Region</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>finnish minerals beijing easpring</t>
+          <t>volvo cars</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4368,10 +4360,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>37.5</v>
+        <v>250000</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>45139</v>
+        <v>44743</v>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
@@ -4382,27 +4374,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Kymenlaakso</t>
+          <t>Košice Region</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>finnish minerals group</t>
+          <t>zhi dou</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4411,10 +4403,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>33.5</v>
+        <v>60000</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>45139</v>
+        <v>43191</v>
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
@@ -4425,42 +4417,42 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Kymenlaakso</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>deployment</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>baywa re</t>
+          <t>easpring finland new materials oy</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>9</v>
+        <v>60000</v>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" s="2" t="n">
-        <v>45566</v>
-      </c>
+      <c r="J99" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="K99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -4468,28 +4460,40 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Kymenlaakso</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>eam</t>
+        </is>
+      </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>lotus</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
+          <t>finnish minerals beijing easpring</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>45139</v>
+      </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
     </row>
@@ -4499,32 +4503,40 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Kymenlaakso</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>electricbrands</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
+          <t>finnish minerals group</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>45139</v>
+      </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
     </row>
@@ -4534,42 +4546,42 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>deployment</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>gotion high tech</t>
+          <t>baywa re</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I102" s="2" t="n">
-        <v>44409</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" s="2" t="n">
+        <v>45566</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -4577,40 +4589,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>module_pack</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>gotion high tech</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H103" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I103" s="2" t="n">
-        <v>44409</v>
-      </c>
+          <t>lotus</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
     </row>
@@ -4630,29 +4630,23 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>graphenix development inc</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>under construction</t>
-        </is>
-      </c>
+          <t>electricbrands</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" s="2" t="n">
-        <v>45292</v>
-      </c>
+      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
@@ -4681,26 +4675,22 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>gotion high tech</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>20</v>
+        <v>3.5</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>44317</v>
-      </c>
-      <c r="J105" s="2" t="n">
-        <v>45627</v>
-      </c>
-      <c r="K105" s="2" t="n">
-        <v>43586</v>
-      </c>
+        <v>44409</v>
+      </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -4723,31 +4713,27 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>gotion high tech</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>20</v>
+        <v>3.5</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>44317</v>
-      </c>
-      <c r="J106" s="2" t="n">
-        <v>45627</v>
-      </c>
-      <c r="K106" s="2" t="n">
-        <v>43586</v>
-      </c>
+        <v>44409</v>
+      </c>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -4765,31 +4751,29 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>graphenix development inc</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H107" t="n">
-        <v>300000</v>
-      </c>
-      <c r="I107" s="2" t="n">
-        <v>43709</v>
-      </c>
-      <c r="J107" t="inlineStr"/>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" s="2" t="n">
+        <v>45292</v>
+      </c>
       <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
@@ -4813,12 +4797,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>recycling</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>volkswagen group components</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4827,12 +4811,16 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>3600</v>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>44317</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>45627</v>
+      </c>
       <c r="K108" s="2" t="n">
-        <v>44197</v>
+        <v>43586</v>
       </c>
     </row>
     <row r="109">
@@ -4856,27 +4844,31 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>volkswagen northvolt</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>16</v>
-      </c>
-      <c r="I109" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>44317</v>
+      </c>
       <c r="J109" s="2" t="n">
-        <v>43709</v>
-      </c>
-      <c r="K109" t="inlineStr"/>
+        <v>45627</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>43586</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -4884,23 +4876,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Lower Silesia</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>lg chem</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4909,10 +4905,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>5</v>
+        <v>300000</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>42644</v>
+        <v>43709</v>
       </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
@@ -4923,12 +4919,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Lower Silesia</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4938,12 +4934,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>lg energy solution</t>
+          <t>volkswagen group components</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4952,12 +4948,12 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>70</v>
+        <v>3600</v>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" s="2" t="n">
-        <v>45261</v>
+        <v>44197</v>
       </c>
     </row>
     <row r="112">
@@ -4966,12 +4962,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Molise</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4986,21 +4982,21 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
+          <t>volkswagen northvolt</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>40</v>
-      </c>
-      <c r="I112" s="2" t="n">
-        <v>45444</v>
-      </c>
-      <c r="J112" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" s="2" t="n">
+        <v>43709</v>
+      </c>
       <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
@@ -5009,12 +5005,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Nitra Region</t>
+          <t>Lower Silesia</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5022,14 +5018,10 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>gotion inobat batteries</t>
+          <t>lg chem</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -5038,10 +5030,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>45231</v>
+        <v>42644</v>
       </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
@@ -5052,12 +5044,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Nordland</t>
+          <t>Lower Silesia</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5067,27 +5059,27 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>freyr</t>
+          <t>lg energy solution</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" s="2" t="n">
-        <v>43678</v>
-      </c>
-      <c r="J114" s="2" t="n">
-        <v>44470</v>
-      </c>
-      <c r="K114" t="inlineStr"/>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>70</v>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" s="2" t="n">
+        <v>45261</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -5095,12 +5087,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Nordland</t>
+          <t>Molise</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5110,26 +5102,26 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>freyr</t>
+          <t>automotive cell company</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>40</v>
+      </c>
       <c r="I115" s="2" t="n">
-        <v>43678</v>
-      </c>
-      <c r="J115" s="2" t="n">
-        <v>44470</v>
-      </c>
+        <v>45444</v>
+      </c>
+      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
@@ -5138,38 +5130,38 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Normandy</t>
+          <t>Murcia</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>hopium</t>
+          <t>china three gorges corporation</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I116" s="2" t="n">
-        <v>44805</v>
-      </c>
+        <v>0.494</v>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" s="2" t="n">
+        <v>45658</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -5177,32 +5169,40 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Normandy</t>
+          <t>Nitra Region</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>renault</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
+          <t>gotion inobat batteries</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>20</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>45231</v>
+      </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
     </row>
@@ -5212,12 +5212,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Nordland</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5227,25 +5227,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>recycling</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>cylib</t>
+          <t>freyr</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" s="2" t="n">
-        <v>45261</v>
-      </c>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>29</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>43678</v>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>44470</v>
+      </c>
+      <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -5253,33 +5257,43 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Nordland</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>ego mobile</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
+          <t>freyr</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>29</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>43678</v>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>44470</v>
+      </c>
       <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
@@ -5288,12 +5302,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Normandy</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5301,19 +5315,23 @@
           <t>vehicle</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>electric</t>
-        </is>
-      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>ford</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
+          <t>hopium</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>44805</v>
+      </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
     </row>
@@ -5323,39 +5341,33 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Normandy</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>fraunhofer ffb</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>under construction</t>
-        </is>
-      </c>
+          <t>renault</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" s="2" t="n">
-        <v>45444</v>
-      </c>
+      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
@@ -5374,32 +5386,30 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>nextego mobile</t>
+          <t>cylib</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H122" t="n">
-        <v>30000</v>
-      </c>
-      <c r="I122" s="2" t="n">
-        <v>45200</v>
-      </c>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" s="2" t="n">
+        <v>45261</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -5417,26 +5427,22 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr"/>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>primobius</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H123" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I123" s="2" t="n">
-        <v>44317</v>
-      </c>
+          <t>ego mobile</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
     </row>
@@ -5456,32 +5462,24 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>pure battery technologies</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H124" t="n">
-        <v>10000</v>
-      </c>
+          <t>ford</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
-      <c r="K124" s="2" t="n">
-        <v>44713</v>
-      </c>
+      <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -5502,10 +5500,14 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>rwth aachen university</t>
+          <t>fraunhofer ffb</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -5516,7 +5518,7 @@
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
       <c r="J125" s="2" t="n">
-        <v>45292</v>
+        <v>45444</v>
       </c>
       <c r="K125" t="inlineStr"/>
     </row>
@@ -5526,43 +5528,41 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Northumberland</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>britishvolt</t>
+          <t>nextego mobile</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>4</v>
+        <v>30000</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>44197</v>
-      </c>
-      <c r="J126" s="2" t="n">
-        <v>44531</v>
-      </c>
+        <v>45200</v>
+      </c>
+      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
     </row>
     <row r="127">
@@ -5571,12 +5571,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Northumberland</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5584,30 +5584,24 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>module_pack</t>
-        </is>
-      </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>britishvolt</t>
+          <t>primobius</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>4</v>
+        <v>20000</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>44197</v>
-      </c>
-      <c r="J127" s="2" t="n">
-        <v>44531</v>
-      </c>
+        <v>44317</v>
+      </c>
+      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
@@ -5616,12 +5610,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Nouvelle-Aquitaine</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -5631,12 +5625,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>forsee power</t>
+          <t>pure battery technologies</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -5645,12 +5639,12 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" s="2" t="n">
-        <v>44986</v>
+        <v>44713</v>
       </c>
     </row>
     <row r="129">
@@ -5659,12 +5653,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Nouvelle-Aquitaine</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -5672,20 +5666,22 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>module_pack</t>
-        </is>
-      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>startec energy</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr"/>
+          <t>rwth aachen university</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
+      <c r="J129" s="2" t="n">
+        <v>45292</v>
+      </c>
       <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
@@ -5694,41 +5690,43 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Novo Mesto</t>
+          <t>Northumberland</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>revoz</t>
+          <t>britishvolt</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>150000</v>
+        <v>4</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>45474</v>
-      </c>
-      <c r="J130" t="inlineStr"/>
+        <v>44197</v>
+      </c>
+      <c r="J130" s="2" t="n">
+        <v>44531</v>
+      </c>
       <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
@@ -5737,41 +5735,43 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Opole Voivodeship</t>
+          <t>Northumberland</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>deployment</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>ox2</t>
+          <t>britishvolt</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>0.09</v>
+        <v>4</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>45839</v>
-      </c>
-      <c r="J131" t="inlineStr"/>
+        <v>44197</v>
+      </c>
+      <c r="J131" s="2" t="n">
+        <v>44531</v>
+      </c>
       <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Opole Voivodeship</t>
+          <t>Nouvelle-Aquitaine</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>umicore</t>
+          <t>forsee power</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5809,12 +5809,12 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
       <c r="K132" s="2" t="n">
-        <v>44958</v>
+        <v>44986</v>
       </c>
     </row>
     <row r="133">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ostrobothnia</t>
+          <t>Nouvelle-Aquitaine</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -5838,25 +5838,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>finnish minerals group epsilon advanced materials</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H133" t="n">
-        <v>50000</v>
-      </c>
-      <c r="I133" s="2" t="n">
-        <v>44866</v>
-      </c>
+          <t>startec energy</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
     </row>
@@ -5866,27 +5858,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ostrobothnia</t>
+          <t>Novo Mesto</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>freyr battery</t>
+          <t>revoz</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5895,10 +5887,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>30000</v>
+        <v>150000</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>45566</v>
+        <v>45474</v>
       </c>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
@@ -5909,27 +5901,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ostrobothnia</t>
+          <t>Opole Voivodeship</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>deployment</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>johnson matthey</t>
+          <t>ox2</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5938,10 +5930,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>30000</v>
+        <v>0.09</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>44287</v>
+        <v>45839</v>
       </c>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
@@ -5952,34 +5944,42 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Opole Voivodeship</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>bmw</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
+          <t>umicore</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>20</v>
+      </c>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" s="2" t="n">
+        <v>44958</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -5987,27 +5987,27 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Ostrobothnia</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>deployment</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>photovolt development partners</t>
+          <t>finnish minerals group epsilon advanced materials</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>0.84</v>
+        <v>50000</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>45778</v>
+        <v>44866</v>
       </c>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
@@ -6030,12 +6030,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Pest County</t>
+          <t>Ostrobothnia</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6045,17 +6045,25 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>samsung sdi</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
+          <t>freyr battery</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>45566</v>
+      </c>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
     </row>
@@ -6065,42 +6073,42 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>Ostrobothnia</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>fiat chrysler</t>
+          <t>johnson matthey</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>80000</v>
-      </c>
-      <c r="I139" t="inlineStr"/>
+        <v>30000</v>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>44287</v>
+      </c>
       <c r="J139" t="inlineStr"/>
-      <c r="K139" s="2" t="n">
-        <v>43862</v>
-      </c>
+      <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -6108,40 +6116,32 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>italvolt</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H140" t="n">
-        <v>45</v>
-      </c>
-      <c r="I140" s="2" t="n">
-        <v>44348</v>
-      </c>
+          <t>bmw</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
     </row>
@@ -6151,42 +6151,42 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>deployment</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>micro mobility</t>
+          <t>photovolt development partners</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>7500</v>
-      </c>
-      <c r="I141" t="inlineStr"/>
+        <v>0.84</v>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>45778</v>
+      </c>
       <c r="J141" t="inlineStr"/>
-      <c r="K141" s="2" t="n">
-        <v>44440</v>
-      </c>
+      <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -6194,23 +6194,27 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>Pest County</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>samsung sdi</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
@@ -6225,42 +6229,42 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Pirkanmaa</t>
+          <t>Piedmont</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>recycling</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>fortum</t>
+          <t>fiat chrysler</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>3000</v>
-      </c>
-      <c r="I143" s="2" t="n">
-        <v>44197</v>
-      </c>
+        <v>80000</v>
+      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" s="2" t="n">
+        <v>43862</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -6268,12 +6272,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Pirkanmaa</t>
+          <t>Piedmont</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -6283,17 +6287,25 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>recycling</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>fortum battery recycling</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr"/>
+          <t>italvolt</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>45</v>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>44348</v>
+      </c>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
     </row>
@@ -6303,40 +6315,42 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Pomerania</t>
+          <t>Piedmont</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>northvolt south bay solutions</t>
+          <t>micro mobility</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" s="2" t="n">
-        <v>43374</v>
-      </c>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" s="2" t="n">
+        <v>44440</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -6344,43 +6358,29 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Rheinland-Pfalz</t>
+          <t>Piedmont</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H146" t="n">
-        <v>8</v>
-      </c>
-      <c r="I146" s="2" t="n">
-        <v>43862</v>
-      </c>
-      <c r="J146" s="2" t="n">
-        <v>44440</v>
-      </c>
+          <t>stellantis</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Rheinland-Pfalz</t>
+          <t>Pirkanmaa</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -6404,28 +6404,26 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
+          <t>fortum</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>8</v>
+        <v>3000</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>43862</v>
-      </c>
-      <c r="J147" s="2" t="n">
-        <v>44440</v>
-      </c>
+        <v>44197</v>
+      </c>
+      <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
     </row>
     <row r="148">
@@ -6434,12 +6432,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Rheinland-Pfalz</t>
+          <t>Pirkanmaa</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -6447,25 +6445,21 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>recycling</t>
+        </is>
+      </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>e lyte</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H148" t="n">
-        <v>20000</v>
-      </c>
+          <t>fortum battery recycling</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
-      <c r="K148" s="2" t="n">
-        <v>45536</v>
-      </c>
+      <c r="K148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -6473,27 +6467,27 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Pomerania</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>deployment</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>sng solar</t>
+          <t>northvolt south bay solutions</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -6501,11 +6495,9 @@
           <t>announced</t>
         </is>
       </c>
-      <c r="H149" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="H149" t="inlineStr"/>
       <c r="I149" s="2" t="n">
-        <v>45839</v>
+        <v>43374</v>
       </c>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
@@ -6516,23 +6508,27 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Ruse</t>
+          <t>Rheinland-Pfalz</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>eberspacher</t>
+          <t>automotive cell company</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -6541,11 +6537,13 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="I150" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>43862</v>
+      </c>
       <c r="J150" s="2" t="n">
-        <v>45017</v>
+        <v>44440</v>
       </c>
       <c r="K150" t="inlineStr"/>
     </row>
@@ -6560,7 +6558,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Saarland</t>
+          <t>Rheinland-Pfalz</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -6570,12 +6568,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>svolt</t>
+          <t>automotive cell company</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -6584,13 +6582,13 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>297</v>
+        <v>8</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>44136</v>
+        <v>43862</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>44531</v>
+        <v>44440</v>
       </c>
       <c r="K151" t="inlineStr"/>
     </row>
@@ -6600,12 +6598,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Sardinia</t>
+          <t>Rheinland-Pfalz</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -6613,29 +6611,25 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>recycling</t>
-        </is>
-      </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>li cycle glencore</t>
+          <t>e lyte</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H152" t="n">
-        <v>60000</v>
-      </c>
-      <c r="I152" s="2" t="n">
-        <v>45139</v>
-      </c>
+        <v>20000</v>
+      </c>
+      <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" s="2" t="n">
+        <v>45536</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -6643,43 +6637,41 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Satakunta</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>deployment</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>basf</t>
+          <t>sng solar</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H153" t="n">
-        <v>20</v>
+        <v>0.1</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>43405</v>
-      </c>
-      <c r="J153" s="2" t="n">
-        <v>43983</v>
-      </c>
+        <v>45536</v>
+      </c>
+      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
@@ -6688,46 +6680,38 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Ruse</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>blackstone technology</t>
+          <t>eberspacher</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H154" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I154" s="2" t="n">
-        <v>44228</v>
-      </c>
+        <v>2400000</v>
+      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="J154" s="2" t="n">
-        <v>44440</v>
-      </c>
-      <c r="K154" s="2" t="n">
-        <v>43466</v>
-      </c>
+        <v>45017</v>
+      </c>
+      <c r="K154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -6740,7 +6724,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Saarland</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -6750,18 +6734,28 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>bmw</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
+          <t>svolt</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
+        <v>297</v>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>44136</v>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>44531</v>
+      </c>
       <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
@@ -6770,32 +6764,40 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Sardinia</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>bmw</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
+          <t>li cycle glencore</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>45139</v>
+      </c>
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
     </row>
@@ -6805,39 +6807,43 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Satakunta</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>ingot_wafer</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>european semiconductor manufacturing company</t>
+          <t>basf</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr"/>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>20</v>
+      </c>
       <c r="I157" s="2" t="n">
-        <v>45627</v>
-      </c>
-      <c r="J157" t="inlineStr"/>
+        <v>43405</v>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>43983</v>
+      </c>
       <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
@@ -6861,19 +6867,31 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>jt energy systems</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr"/>
-      <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
+          <t>blackstone technology</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H158" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>44228</v>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>44440</v>
+      </c>
+      <c r="K158" s="2" t="n">
+        <v>43466</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -6891,17 +6909,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>meyer burger</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="G159" t="inlineStr"/>
@@ -6936,20 +6954,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>volkswagen</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H160" t="n">
-        <v>109500</v>
-      </c>
-      <c r="I160" s="2" t="n">
-        <v>42856</v>
-      </c>
+          <t>bmw</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
     </row>
@@ -6964,36 +6974,34 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>ingot_wafer</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>amg lithium</t>
+          <t>european semiconductor manufacturing company</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H161" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" s="2" t="n">
-        <v>45047</v>
-      </c>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" s="2" t="n">
+        <v>45627</v>
+      </c>
+      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
     </row>
     <row r="162">
@@ -7007,7 +7015,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7015,25 +7023,21 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>module_pack</t>
+        </is>
+      </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>battery lifecycle company</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="H162" t="n">
-        <v>15000</v>
-      </c>
+          <t>jt energy systems</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr"/>
-      <c r="K162" s="2" t="n">
-        <v>45505</v>
-      </c>
+      <c r="K162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -7046,12 +7050,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -7061,18 +7065,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>farasis energy</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
+          <t>meyer burger</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr"/>
-      <c r="I163" s="2" t="n">
-        <v>44228</v>
-      </c>
+      <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
     </row>
@@ -7087,22 +7085,18 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>farasis energy europe</t>
+          <t>solarwatt</t>
         </is>
       </c>
       <c r="G164" t="inlineStr"/>
@@ -7122,39 +7116,37 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>recycling</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>li cycle</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H165" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" s="2" t="n">
-        <v>44986</v>
-      </c>
-      <c r="K165" s="2" t="n">
-        <v>45139</v>
-      </c>
+        <v>109500</v>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>42856</v>
+      </c>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -7182,7 +7174,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>norcsi</t>
+          <t>amg lithium</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -7190,10 +7182,12 @@
           <t>under construction</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr"/>
+      <c r="H166" t="n">
+        <v>20000</v>
+      </c>
       <c r="I166" t="inlineStr"/>
       <c r="J166" s="2" t="n">
-        <v>45839</v>
+        <v>45047</v>
       </c>
       <c r="K166" t="inlineStr"/>
     </row>
@@ -7208,7 +7202,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Schleswig-Holstein</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -7216,31 +7210,25 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
+      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
-          <t>northvolt</t>
+          <t>battery lifecycle company</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H167" t="n">
-        <v>15</v>
-      </c>
-      <c r="I167" s="2" t="n">
-        <v>44621</v>
-      </c>
-      <c r="J167" s="2" t="n">
-        <v>45352</v>
-      </c>
-      <c r="K167" t="inlineStr"/>
+        <v>15000</v>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" s="2" t="n">
+        <v>45505</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -7248,12 +7236,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Schwyz</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -7261,24 +7249,26 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>ecovolta</t>
+          <t>farasis energy</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H168" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" s="2" t="n">
-        <v>43252</v>
-      </c>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" s="2" t="n">
+        <v>44228</v>
+      </c>
+      <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
     </row>
     <row r="169">
@@ -7287,12 +7277,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -7307,20 +7297,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>calb</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H169" t="n">
-        <v>15</v>
-      </c>
-      <c r="I169" s="2" t="n">
-        <v>44866</v>
-      </c>
+          <t>farasis energy europe</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
     </row>
@@ -7330,12 +7312,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -7345,27 +7327,29 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>calb</t>
+          <t>li cycle</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H170" t="n">
-        <v>15</v>
-      </c>
-      <c r="I170" s="2" t="n">
-        <v>44866</v>
-      </c>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
+        <v>10000</v>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" s="2" t="n">
+        <v>44986</v>
+      </c>
+      <c r="K170" s="2" t="n">
+        <v>45139</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
@@ -7373,37 +7357,39 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>eam</t>
+        </is>
+      </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>norcsi</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H171" t="n">
-        <v>100000</v>
-      </c>
-      <c r="I171" s="2" t="n">
-        <v>45748</v>
-      </c>
-      <c r="J171" t="inlineStr"/>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" s="2" t="n">
+        <v>45839</v>
+      </c>
       <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
@@ -7412,12 +7398,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Silesia</t>
+          <t>Schleswig-Holstein</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -7427,29 +7413,29 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>recycling</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>ae elemental</t>
+          <t>northvolt</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H172" t="n">
-        <v>12000</v>
+        <v>15</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>45383</v>
-      </c>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" s="2" t="n">
-        <v>45536</v>
-      </c>
+        <v>44621</v>
+      </c>
+      <c r="J172" s="2" t="n">
+        <v>45352</v>
+      </c>
+      <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -7457,37 +7443,37 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Silesia</t>
+          <t>Schwyz</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>ecovolta</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H173" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I173" s="2" t="n">
-        <v>44958</v>
-      </c>
-      <c r="J173" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" s="2" t="n">
+        <v>43252</v>
+      </c>
       <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
@@ -7496,12 +7482,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Solothurn</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -7511,27 +7497,27 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>recycling</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>librec</t>
+          <t>calb</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H174" t="n">
-        <v>12000</v>
-      </c>
-      <c r="I174" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>44866</v>
+      </c>
       <c r="J174" t="inlineStr"/>
-      <c r="K174" s="2" t="n">
-        <v>45778</v>
-      </c>
+      <c r="K174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
@@ -7539,12 +7525,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -7554,28 +7540,26 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>agratas</t>
+          <t>calb</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H175" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>45108</v>
-      </c>
-      <c r="J175" s="2" t="n">
-        <v>45689</v>
-      </c>
+        <v>44866</v>
+      </c>
+      <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
@@ -7584,32 +7568,36 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Southwest Finland</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>module_pack</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>valmet automotive</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr"/>
+          <t>volkswagen</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H176" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>45748</v>
+      </c>
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
     </row>
@@ -7619,38 +7607,44 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Southwest Finland</t>
+          <t>Silesia</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>recycling</t>
+        </is>
+      </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>valmet automotive</t>
+          <t>ae elemental</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H177" t="n">
-        <v>257000</v>
+        <v>12000</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>44652</v>
+        <v>45383</v>
       </c>
       <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" s="2" t="n">
+        <v>45536</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
@@ -7658,12 +7652,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>State of Berlin</t>
+          <t>Silesia</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -7671,19 +7665,23 @@
           <t>vehicle</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>electric</t>
-        </is>
-      </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>tesla</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
+          <t>stellantis</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H178" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>44958</v>
+      </c>
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
     </row>
@@ -7693,12 +7691,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Solothurn</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -7708,12 +7706,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>aesc</t>
+          <t>librec</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -7722,16 +7720,12 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I179" s="2" t="n">
-        <v>44317</v>
-      </c>
-      <c r="J179" s="2" t="n">
-        <v>44470</v>
-      </c>
+        <v>12000</v>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
       <c r="K179" s="2" t="n">
-        <v>45292</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="180">
@@ -7745,7 +7739,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -7755,31 +7749,29 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>aesc</t>
+          <t>agratas</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H180" t="n">
-        <v>1.8</v>
+        <v>40</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>44317</v>
+        <v>45108</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>44470</v>
-      </c>
-      <c r="K180" s="2" t="n">
-        <v>45292</v>
-      </c>
+        <v>45689</v>
+      </c>
+      <c r="K180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
@@ -7787,12 +7779,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Southwest Finland</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -7802,28 +7794,18 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>nissan</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H181" t="n">
-        <v>35</v>
-      </c>
-      <c r="I181" s="2" t="n">
-        <v>44896</v>
-      </c>
-      <c r="J181" s="2" t="n">
-        <v>45231</v>
-      </c>
+          <t>valmet automotive</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
@@ -7832,12 +7814,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Southwest Finland</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -7845,28 +7827,24 @@
           <t>vehicle</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>electric</t>
-        </is>
-      </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>nissan</t>
+          <t>valmet automotive</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr"/>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H182" t="n">
+        <v>257000</v>
+      </c>
       <c r="I182" s="2" t="n">
-        <v>44378</v>
-      </c>
-      <c r="J182" s="2" t="n">
-        <v>45352</v>
-      </c>
+        <v>44652</v>
+      </c>
+      <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
@@ -7875,12 +7853,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>State of Berlin</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -7888,10 +7866,14 @@
           <t>vehicle</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>saietta group</t>
+          <t>tesla</t>
         </is>
       </c>
       <c r="G183" t="inlineStr"/>
@@ -7906,12 +7888,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Telemark</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -7921,12 +7903,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>vianode</t>
+          <t>aesc</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -7935,12 +7917,16 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
+        <v>1.8</v>
+      </c>
+      <c r="I184" s="2" t="n">
+        <v>44317</v>
+      </c>
+      <c r="J184" s="2" t="n">
+        <v>44470</v>
+      </c>
       <c r="K184" s="2" t="n">
-        <v>45566</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="185">
@@ -7949,12 +7935,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Thuringia</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -7964,12 +7950,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>catl</t>
+          <t>aesc</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -7978,14 +7964,16 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>8</v>
+        <v>1.8</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>43282</v>
-      </c>
-      <c r="J185" t="inlineStr"/>
+        <v>44317</v>
+      </c>
+      <c r="J185" s="2" t="n">
+        <v>44470</v>
+      </c>
       <c r="K185" s="2" t="n">
-        <v>44501</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="186">
@@ -7994,12 +7982,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Thuringia</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -8009,12 +7997,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>lion smart</t>
+          <t>nissan</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -8022,10 +8010,14 @@
           <t>under construction</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
+      <c r="H186" t="n">
+        <v>35</v>
+      </c>
+      <c r="I186" s="2" t="n">
+        <v>44896</v>
+      </c>
       <c r="J186" s="2" t="n">
-        <v>45139</v>
+        <v>45231</v>
       </c>
       <c r="K186" t="inlineStr"/>
     </row>
@@ -8035,41 +8027,41 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Thuringia</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>recycling</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>sungeel hitech and samsung</t>
+          <t>nissan</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H187" t="n">
-        <v>20000</v>
-      </c>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr"/>
       <c r="I187" s="2" t="n">
-        <v>45170</v>
-      </c>
-      <c r="J187" t="inlineStr"/>
+        <v>44378</v>
+      </c>
+      <c r="J187" s="2" t="n">
+        <v>45352</v>
+      </c>
       <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
@@ -8078,40 +8070,28 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Trnava Region</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>cell</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>gotion inobat batteries</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="H188" t="n">
-        <v>20</v>
-      </c>
-      <c r="I188" s="2" t="n">
-        <v>45261</v>
-      </c>
+          <t>saietta group</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr"/>
     </row>
@@ -8121,12 +8101,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Trnava Region</t>
+          <t>Telemark</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -8136,12 +8116,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>eam</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>inobat</t>
+          <t>vianode</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -8149,15 +8129,13 @@
           <t>operational</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr"/>
-      <c r="I189" s="2" t="n">
-        <v>44105</v>
-      </c>
-      <c r="J189" s="2" t="n">
-        <v>44317</v>
-      </c>
+      <c r="H189" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
       <c r="K189" s="2" t="n">
-        <v>45261</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="190">
@@ -8166,12 +8144,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Trnava Region</t>
+          <t>Thuringia</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -8181,12 +8159,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>inobat</t>
+          <t>catl</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -8194,15 +8172,15 @@
           <t>operational</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr"/>
+      <c r="H190" t="n">
+        <v>8</v>
+      </c>
       <c r="I190" s="2" t="n">
-        <v>44105</v>
-      </c>
-      <c r="J190" s="2" t="n">
-        <v>44317</v>
-      </c>
+        <v>43282</v>
+      </c>
+      <c r="J190" t="inlineStr"/>
       <c r="K190" s="2" t="n">
-        <v>45261</v>
+        <v>44501</v>
       </c>
     </row>
     <row r="191">
@@ -8211,12 +8189,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Trøndelag</t>
+          <t>Thuringia</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -8226,24 +8204,24 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>elinor batteries</t>
+          <t>lion smart</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
-      <c r="I191" s="2" t="n">
-        <v>44927</v>
-      </c>
-      <c r="J191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" s="2" t="n">
+        <v>45139</v>
+      </c>
       <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
@@ -8252,27 +8230,27 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Tukums Municipality</t>
+          <t>Thuringia</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>deployment</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>ignitis renewables</t>
+          <t>sungeel hitech and samsung</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -8281,10 +8259,10 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>0.174</v>
+        <v>20000</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>45839</v>
+        <v>45170</v>
       </c>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr"/>
@@ -8295,37 +8273,41 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Utena</t>
+          <t>Trnava Region</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>solar</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr"/>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>european energy</t>
+          <t>gotion inobat batteries</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H193" t="n">
-        <v>0.0785</v>
-      </c>
-      <c r="I193" t="inlineStr"/>
-      <c r="J193" s="2" t="n">
-        <v>45809</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I193" s="2" t="n">
+        <v>45261</v>
+      </c>
+      <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
@@ -8334,12 +8316,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Trnava Region</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -8354,24 +8336,24 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>inobat</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H194" t="n">
-        <v>40</v>
-      </c>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
       <c r="I194" s="2" t="n">
-        <v>44593</v>
+        <v>44105</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>45566</v>
-      </c>
-      <c r="K194" t="inlineStr"/>
+        <v>44317</v>
+      </c>
+      <c r="K194" s="2" t="n">
+        <v>45261</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
@@ -8379,12 +8361,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Trnava Region</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -8394,29 +8376,29 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>eam</t>
+          <t>module_pack</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>inobat</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H195" t="n">
-        <v>40</v>
-      </c>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
       <c r="I195" s="2" t="n">
-        <v>44593</v>
+        <v>44105</v>
       </c>
       <c r="J195" s="2" t="n">
-        <v>45566</v>
-      </c>
-      <c r="K195" t="inlineStr"/>
+        <v>44317</v>
+      </c>
+      <c r="K195" s="2" t="n">
+        <v>45261</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
@@ -8424,27 +8406,27 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Trøndelag</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>elinor batteries</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -8452,9 +8434,7 @@
           <t>announced</t>
         </is>
       </c>
-      <c r="H196" t="n">
-        <v>40</v>
-      </c>
+      <c r="H196" t="inlineStr"/>
       <c r="I196" s="2" t="n">
         <v>44927</v>
       </c>
@@ -8467,37 +8447,41 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Vas County</t>
+          <t>Tukums Municipality</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr"/>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>schaeffler</t>
+          <t>ignitis renewables</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H197" t="n">
-        <v>800000</v>
-      </c>
-      <c r="I197" t="inlineStr"/>
-      <c r="J197" s="2" t="n">
-        <v>44440</v>
-      </c>
+        <v>0.174</v>
+      </c>
+      <c r="I197" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
@@ -8506,33 +8490,37 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Viseu</t>
+          <t>Utena</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>electric</t>
-        </is>
-      </c>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>stellantis</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr"/>
-      <c r="H198" t="inlineStr"/>
+          <t>european energy</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H198" t="n">
+        <v>0.0785</v>
+      </c>
       <c r="I198" t="inlineStr"/>
-      <c r="J198" t="inlineStr"/>
+      <c r="J198" s="2" t="n">
+        <v>45809</v>
+      </c>
       <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
@@ -8541,42 +8529,38 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Warwickshire</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>electric</t>
-        </is>
-      </c>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
-          <t>london taxi company</t>
+          <t>pv hardware</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H199" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I199" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="I199" s="2" t="n">
+        <v>44958</v>
+      </c>
       <c r="J199" t="inlineStr"/>
-      <c r="K199" s="2" t="n">
-        <v>42795</v>
-      </c>
+      <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
@@ -8584,12 +8568,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Wolverhampton</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -8599,27 +8583,29 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>recycling</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>recyclus group</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H200" t="n">
-        <v>22000</v>
-      </c>
-      <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
-      <c r="K200" s="2" t="n">
-        <v>45200</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="I200" s="2" t="n">
+        <v>44593</v>
+      </c>
+      <c r="J200" s="2" t="n">
+        <v>45566</v>
+      </c>
+      <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
@@ -8627,12 +8613,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -8640,25 +8626,31 @@
           <t>battery</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>eam</t>
+        </is>
+      </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>battrion</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H201" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
-      <c r="K201" s="2" t="n">
-        <v>44287</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="I201" s="2" t="n">
+        <v>44593</v>
+      </c>
+      <c r="J201" s="2" t="n">
+        <v>45566</v>
+      </c>
+      <c r="K201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
@@ -8666,27 +8658,27 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Île-de-France</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>recycling</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>lg energy solution derichebourg</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -8695,10 +8687,10 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>20000</v>
+        <v>40</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>45748</v>
+        <v>44927</v>
       </c>
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr"/>
@@ -8709,44 +8701,38 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Østfold</t>
+          <t>Vas County</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>recycling</t>
-        </is>
-      </c>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>hydrovolt</t>
+          <t>schaeffler</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H203" t="n">
-        <v>12000</v>
+        <v>800000</v>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="J203" s="2" t="n">
-        <v>44228</v>
-      </c>
-      <c r="K203" s="2" t="n">
-        <v>44228</v>
-      </c>
+        <v>44440</v>
+      </c>
+      <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
@@ -8754,38 +8740,329 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Świętokrzyskie</t>
+          <t>Viseu</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>module_pack</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>green cell</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
+          <t>stellantis</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr"/>
-      <c r="K204" s="2" t="n">
+      <c r="K204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>203</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Warwickshire</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>london taxi company</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H205" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" s="2" t="n">
+        <v>42795</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>204</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Warwickshire</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>moke international</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H206" t="n">
+        <v>500</v>
+      </c>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" s="2" t="n">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>205</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Wolverhampton</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>recycling</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>recyclus group</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H207" t="n">
+        <v>22000</v>
+      </c>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" s="2" t="n">
+        <v>45200</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>206</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>battrion</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H208" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" s="2" t="n">
+        <v>44287</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>207</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Île-de-France</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>recycling</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>lg energy solution derichebourg</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="H209" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I209" s="2" t="n">
+        <v>45748</v>
+      </c>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>208</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Østfold</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>recycling</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>hydrovolt</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H210" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" s="2" t="n">
+        <v>44228</v>
+      </c>
+      <c r="K210" s="2" t="n">
+        <v>44228</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>209</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Świętokrzyskie</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>module_pack</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>green cell</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" s="2" t="n">
         <v>44652</v>
       </c>
     </row>

--- a/reconcile/storage/output/capacities_plot.xlsx
+++ b/reconcile/storage/output/capacities_plot.xlsx
@@ -23389,7 +23389,7 @@
         <v>0.4</v>
       </c>
       <c r="M448" s="2" t="n">
-        <v>44287</v>
+        <v>45323</v>
       </c>
       <c r="N448" s="2" t="n">
         <v>44197</v>
@@ -23450,7 +23450,7 @@
         <v>0.4</v>
       </c>
       <c r="M449" s="2" t="n">
-        <v>44287</v>
+        <v>45323</v>
       </c>
       <c r="N449" s="2" t="n">
         <v>44197</v>
@@ -23928,9 +23928,7 @@
       <c r="L458" t="n">
         <v>0.4</v>
       </c>
-      <c r="M458" s="2" t="n">
-        <v>44287</v>
-      </c>
+      <c r="M458" t="inlineStr"/>
       <c r="N458" s="2" t="n">
         <v>44197</v>
       </c>
@@ -23985,9 +23983,7 @@
       <c r="L459" t="n">
         <v>0.4</v>
       </c>
-      <c r="M459" s="2" t="n">
-        <v>44287</v>
-      </c>
+      <c r="M459" t="inlineStr"/>
       <c r="N459" s="2" t="n">
         <v>44197</v>
       </c>

--- a/reconcile/storage/output/capacities_plot.xlsx
+++ b/reconcile/storage/output/capacities_plot.xlsx
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" s="2" t="n">
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>44958</v>
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>44958</v>
@@ -2881,7 +2881,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.85</v>
+        <v>0.16</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>45444</v>
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>250000</v>
+        <v>360000</v>
       </c>
       <c r="H108" t="inlineStr"/>
       <c r="I108" s="2" t="n">
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="H127" s="2" t="n">
         <v>44197</v>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="H128" s="2" t="n">
         <v>44197</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>0.28</v>
+        <v>0.21</v>
       </c>
       <c r="H131" s="2" t="n">
         <v>45139</v>
@@ -6328,7 +6328,9 @@
           <t>under construction</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr"/>
+      <c r="G178" t="n">
+        <v>29</v>
+      </c>
       <c r="H178" s="2" t="n">
         <v>44470</v>
       </c>
@@ -6365,7 +6367,9 @@
           <t>under construction</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr"/>
+      <c r="G179" t="n">
+        <v>29</v>
+      </c>
       <c r="H179" s="2" t="n">
         <v>44470</v>
       </c>
@@ -6725,7 +6729,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="H190" t="inlineStr"/>
       <c r="I190" s="2" t="n">
@@ -7927,7 +7931,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>200000</v>
+        <v>40000</v>
       </c>
       <c r="H224" s="2" t="n">
         <v>45689</v>
@@ -7968,7 +7972,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>200000</v>
+        <v>40000</v>
       </c>
       <c r="H225" s="2" t="n">
         <v>45689</v>
@@ -13137,7 +13141,7 @@
         </is>
       </c>
       <c r="G382" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H382" s="2" t="n">
         <v>43739</v>
@@ -13178,7 +13182,7 @@
         </is>
       </c>
       <c r="G383" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H383" s="2" t="n">
         <v>43739</v>
@@ -13219,7 +13223,7 @@
         </is>
       </c>
       <c r="G384" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H384" s="2" t="n">
         <v>43739</v>
@@ -21170,7 +21174,7 @@
         </is>
       </c>
       <c r="G625" t="n">
-        <v>0.147</v>
+        <v>1.5</v>
       </c>
       <c r="H625" t="inlineStr"/>
       <c r="I625" s="2" t="n">
@@ -21664,7 +21668,7 @@
         </is>
       </c>
       <c r="G639" t="n">
-        <v>0.134</v>
+        <v>0.112</v>
       </c>
       <c r="H639" t="inlineStr"/>
       <c r="I639" s="2" t="n">
@@ -23573,10 +23577,18 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="F696" t="inlineStr"/>
-      <c r="G696" t="inlineStr"/>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="G696" t="n">
+        <v>40000</v>
+      </c>
       <c r="H696" t="inlineStr"/>
-      <c r="I696" t="inlineStr"/>
+      <c r="I696" s="2" t="n">
+        <v>45657</v>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -24291,10 +24303,18 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="F718" t="inlineStr"/>
-      <c r="G718" t="inlineStr"/>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="G718" t="n">
+        <v>40000</v>
+      </c>
       <c r="H718" t="inlineStr"/>
-      <c r="I718" t="inlineStr"/>
+      <c r="I718" s="2" t="n">
+        <v>45657</v>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
@@ -24460,7 +24480,7 @@
         </is>
       </c>
       <c r="G723" t="n">
-        <v>50000</v>
+        <v>40000</v>
       </c>
       <c r="H723" t="inlineStr"/>
       <c r="I723" s="2" t="n">
@@ -25426,7 +25446,7 @@
         </is>
       </c>
       <c r="G753" t="n">
-        <v>156831.93</v>
+        <v>240000</v>
       </c>
       <c r="H753" t="inlineStr"/>
       <c r="I753" s="2" t="n">
@@ -25661,7 +25681,7 @@
         </is>
       </c>
       <c r="G760" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="H760" s="2" t="n">
         <v>44531</v>
@@ -25700,7 +25720,7 @@
         </is>
       </c>
       <c r="G761" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="H761" s="2" t="n">
         <v>44531</v>
@@ -27834,7 +27854,7 @@
         </is>
       </c>
       <c r="G827" t="n">
-        <v>400000</v>
+        <v>80000</v>
       </c>
       <c r="H827" t="inlineStr"/>
       <c r="I827" s="2" t="n">
@@ -30277,7 +30297,7 @@
         </is>
       </c>
       <c r="G902" t="n">
-        <v>0.05</v>
+        <v>0.5</v>
       </c>
       <c r="H902" s="2" t="n">
         <v>44440</v>
@@ -31008,7 +31028,7 @@
         </is>
       </c>
       <c r="G925" t="n">
-        <v>200000</v>
+        <v>80000</v>
       </c>
       <c r="H925" t="inlineStr"/>
       <c r="I925" s="2" t="n">
@@ -31216,7 +31236,7 @@
         </is>
       </c>
       <c r="G931" t="n">
-        <v>1250</v>
+        <v>1000</v>
       </c>
       <c r="H931" s="2" t="n">
         <v>42552</v>
@@ -32507,7 +32527,7 @@
         </is>
       </c>
       <c r="G970" t="n">
-        <v>28334</v>
+        <v>40000</v>
       </c>
       <c r="H970" t="inlineStr"/>
       <c r="I970" s="2" t="n">
@@ -33451,7 +33471,7 @@
         </is>
       </c>
       <c r="G998" t="n">
-        <v>35000</v>
+        <v>36500</v>
       </c>
       <c r="H998" t="inlineStr"/>
       <c r="I998" s="2" t="n">
@@ -34274,7 +34294,7 @@
         </is>
       </c>
       <c r="G1023" t="n">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="H1023" s="2" t="n">
         <v>44228</v>
@@ -35944,7 +35964,7 @@
         </is>
       </c>
       <c r="G1075" t="n">
-        <v>12</v>
+        <v>1.8</v>
       </c>
       <c r="H1075" s="2" t="n">
         <v>44470</v>
@@ -35985,7 +36005,7 @@
         </is>
       </c>
       <c r="G1076" t="n">
-        <v>12</v>
+        <v>1.8</v>
       </c>
       <c r="H1076" s="2" t="n">
         <v>44470</v>
@@ -37631,7 +37651,7 @@
         </is>
       </c>
       <c r="G1126" t="n">
-        <v>0.3</v>
+        <v>0.014</v>
       </c>
       <c r="H1126" s="2" t="n">
         <v>44531</v>
@@ -38913,7 +38933,7 @@
         </is>
       </c>
       <c r="G1164" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H1164" t="inlineStr"/>
       <c r="I1164" s="2" t="n">
@@ -38952,7 +38972,7 @@
         </is>
       </c>
       <c r="G1165" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H1165" t="inlineStr"/>
       <c r="I1165" s="2" t="n">
@@ -39424,7 +39444,7 @@
         </is>
       </c>
       <c r="G1179" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H1179" s="2" t="n">
         <v>45170</v>
@@ -39465,7 +39485,7 @@
         </is>
       </c>
       <c r="G1180" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H1180" s="2" t="n">
         <v>45170</v>
@@ -41180,7 +41200,7 @@
         </is>
       </c>
       <c r="G1231" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="H1231" s="2" t="n">
         <v>43709</v>
@@ -41221,7 +41241,7 @@
         </is>
       </c>
       <c r="G1232" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="H1232" s="2" t="n">
         <v>43709</v>
@@ -41262,7 +41282,7 @@
         </is>
       </c>
       <c r="G1233" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="H1233" s="2" t="n">
         <v>43709</v>
@@ -43009,7 +43029,7 @@
         </is>
       </c>
       <c r="G1288" t="n">
-        <v>50</v>
+        <v>300000</v>
       </c>
       <c r="H1288" t="inlineStr"/>
       <c r="I1288" s="2" t="n">
@@ -45676,7 +45696,7 @@
         </is>
       </c>
       <c r="G1367" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="H1367" s="2" t="n">
         <v>45139</v>
@@ -45715,7 +45735,7 @@
         </is>
       </c>
       <c r="G1368" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="H1368" s="2" t="n">
         <v>45139</v>
@@ -45754,7 +45774,7 @@
         </is>
       </c>
       <c r="G1369" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="H1369" s="2" t="n">
         <v>45139</v>
@@ -45793,7 +45813,7 @@
         </is>
       </c>
       <c r="G1370" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="H1370" s="2" t="n">
         <v>45139</v>
@@ -45832,7 +45852,7 @@
         </is>
       </c>
       <c r="G1371" t="n">
-        <v>5e-05</v>
+        <v>15</v>
       </c>
       <c r="H1371" s="2" t="n">
         <v>45170</v>
@@ -46814,7 +46834,7 @@
         </is>
       </c>
       <c r="G1401" t="n">
-        <v>0.0864</v>
+        <v>0.59</v>
       </c>
       <c r="H1401" s="2" t="n">
         <v>44774</v>
@@ -46855,7 +46875,7 @@
         </is>
       </c>
       <c r="G1402" t="n">
-        <v>0.0864</v>
+        <v>0.59</v>
       </c>
       <c r="H1402" s="2" t="n">
         <v>44774</v>
@@ -49557,14 +49577,16 @@
       </c>
       <c r="F1484" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G1484" t="n">
-        <v>300000</v>
+        <v>180000</v>
       </c>
       <c r="H1484" t="inlineStr"/>
-      <c r="I1484" t="inlineStr"/>
+      <c r="I1484" s="2" t="n">
+        <v>45657</v>
+      </c>
     </row>
     <row r="1485">
       <c r="A1485" t="inlineStr">
@@ -49744,7 +49766,7 @@
         </is>
       </c>
       <c r="G1489" t="n">
-        <v>27.375</v>
+        <v>12.5</v>
       </c>
       <c r="H1489" t="inlineStr"/>
       <c r="I1489" s="2" t="n">
@@ -53095,7 +53117,7 @@
         </is>
       </c>
       <c r="G1590" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H1590" s="2" t="n">
         <v>44774</v>
@@ -54286,7 +54308,7 @@
       </c>
       <c r="H1625" t="inlineStr"/>
       <c r="I1625" s="2" t="n">
-        <v>45505</v>
+        <v>45291</v>
       </c>
     </row>
     <row r="1626">
@@ -54428,7 +54450,7 @@
         </is>
       </c>
       <c r="G1629" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H1629" t="inlineStr"/>
       <c r="I1629" s="2" t="n">
@@ -54708,7 +54730,7 @@
         </is>
       </c>
       <c r="G1637" t="n">
-        <v>15000</v>
+        <v>20</v>
       </c>
       <c r="H1637" s="2" t="n">
         <v>43983</v>
@@ -55015,7 +55037,7 @@
         </is>
       </c>
       <c r="G1646" t="n">
-        <v>15411</v>
+        <v>20000</v>
       </c>
       <c r="H1646" t="inlineStr"/>
       <c r="I1646" s="2" t="n">
@@ -56566,7 +56588,7 @@
         </is>
       </c>
       <c r="G1695" t="n">
-        <v>400000</v>
+        <v>120000</v>
       </c>
       <c r="H1695" s="2" t="n">
         <v>44440</v>
@@ -57514,7 +57536,7 @@
         </is>
       </c>
       <c r="G1723" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="H1723" t="inlineStr"/>
       <c r="I1723" s="2" t="n">
